--- a/scripts/data/faq_seed.xlsx
+++ b/scripts/data/faq_seed.xlsx
@@ -420,16 +420,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:O190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,20 +458,60 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_uz</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>answer_uz</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>question_cyr</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>answer_cyr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>question_ru</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>answer_ru</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>question_en</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>answer_en</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>question_zh</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>answer_zh</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>source_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_id</t>
         </is>
@@ -493,8 +541,48 @@
           <t>To'lov tasdiqlangandan so'ng sotuvchidan omborga yetkazish odatda 3–7 ish kuni oladi. Xitoydan O'zbekistonga yetkazish esa 12–20 kun (ba'zan chegara yoki bayramlarda 25 kungacha). Jami taxminan 15–25 kun ichida yetkazilishi kutiladi.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма қачон етиб келади?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов тасдиқлангандан сўнг сотувчидан омборга етказиш одатда 3–7 иш куни олади. Хитойдан Ўзбекистонга етказиш эса 12–20 кун (баъзан чегара ёки байрамларда 25 кунгача). Жами тахминан 15–25 кун ичида етказилиши кутилади.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Когда прибудет заказ?</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>После подтверждения оплаты доставка от продавца на склад обычно занимает 3–7 рабочих дней. Доставка из Китая в Узбекистан — 12–20 дней (иногда до 25 дней из-за границы или праздников). В общей сложности ожидается 15–25 дней.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>When will the order arrive?</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>After payment confirmation, delivery from seller to warehouse usually takes 3–7 business days. Delivery from China to Uzbekistan takes 12–20 days (sometimes up to 25 days due to borders or holidays). Total expected time is 15–25 days.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>订单什么时候到？</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款确认后，从卖家到仓库通常需要3-7个工作日。从中国到乌兹别克斯坦需12-20天（有时因边境或节日最多25天）。总计预计15-25天。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -520,8 +608,48 @@
           <t>Bu odatiy holat. Sotuvchi tovarni omborga yetkazgandan keyin holat yangilanadi. Bayram kunlarida yoki chegara yuklamalarida kechikish bo'lishi mumkin. Buyurtma raqamini yuborsangiz aniq holatni tekshirib beramiz.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Нега буюртмам ҳали "Йўлда" ёки "Жўнатиш кутилмоқда" ҳолатида турибди?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Бу одатий ҳолат. Сотувчи товарни омборга етказгандан кейин ҳолат янгиланади. Байрам кунларида ёки чегара юкламаларида кечикиш бўлиши мумкин. Буюртма рақамини юборсангиз аниқ ҳолатни текшириб берамиз.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Почему мой заказ всё ещё в статусе "В пути" или "Ожидается отправка"?</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Это обычная ситуация. Статус обновится после того, как продавец доставит товар на склад. Задержки возможны в праздничные дни или при загруженности границы. Отправьте номер заказа, мы проверим точный статус.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Why is my order still in "On the way" or "Awaiting shipment" status?</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>This is a normal situation. The status will update after the seller delivers the goods to the warehouse. Delays may occur during holidays or border congestion. Send your order number and we will check the exact status.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>为什么我的订单还在“在途”或“等待发货”状态？</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>这是正常情况。卖家将货物送到仓库后状态会更新。节假日或边境繁忙时可能延迟。请发送订单号，我们会检查确切状态。</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -547,8 +675,48 @@
           <t>Ha, yangilangan Sahiy ilovasi orqali buyurtma berganingizda punktgacha yetkazib berish bepul amalga oshiriladi.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Пунктгача етказиб бериш бепулми?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, янгиланган Саҳий иловаси орқали буюртма берганингизда пунктгача етказиб бериш бепул амалга оширилади.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Доставка до пункта бесплатная?</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Да, при оформлении заказа через обновлённое приложение Sahiy доставка до пункта выдачи бесплатная.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Is delivery to the pickup point free?</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Yes, when you place an order through the updated Sahiy app, delivery to the pickup point is free.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>送到自提点免费吗？</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>是的，通过更新后的Sahiy应用下单，送到自提点免费。</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -574,8 +742,48 @@
           <t>Faqat Toshkent shahri va Toshkent viloyati uchun mavjud. Boshqa viloyatlar uchun punkt yoki pochta orqali yetkaziladi.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Уй манзилимгача етказиб бериш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Фақат Тошкент шаҳри ва Тошкент вилояти учун мавжуд. Бошқа вилоятлар учун пункт ёки почта орқали етказилади.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли доставить до адреса домой?</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Доступно только для города Ташкент и Ташкентской области. В другие регионы доставка осуществляется до пункта или через почту.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Is home delivery possible?</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Available only for Tashkent city and Tashkent region. For other regions, delivery is to a pickup point or via post.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>可以送到家吗？</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>仅限塔什干市和塔什干州可用。其他地区通过自提点或邮局配送。</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -601,8 +809,48 @@
           <t>Viloyatlarda doimiy punktlarimiz yo'q. Buyurtmalar Toshkentga kelgandan keyin pochta xizmati (EMU, BTS va boshqalar) orqali yuboriladi.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Вилоятларда пункт борми?</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Вилоятларда доимий пунктларимиз йўқ. Буюртмалар Тошкентга келгандан кейин почта хизмати (EMU, BTS ва бошқалар) орқали юборилади.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Есть ли пункты в регионах?</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>В регионах у нас нет постоянных пунктов. Заказы отправляются через почтовые службы после прибытия в Ташкент.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Are there pickup points in the regions?</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>We do not have permanent pickup points in the regions. Orders are sent via postal services after arriving in Tashkent.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>地区有自提点吗？</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>我们在地区没有固定自提点。订单到达塔什干后通过邮政服务发送。</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -628,8 +876,48 @@
           <t>Kechikish uchun uzr so'raymiz. Buyurtma DG raqam(lar)ini yuboring — mutaxassislarimiz sotuvchi bilan bog'lanib holatni tekshiradi va yechim taklif qiladi.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмам 20-30 кундан ортиқ кечикибмоқда, нима қилай?</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Кечикиш учун узр сўраймиз. Буюртма DG рақам(лар)ини юборинг — мутахассисларимиз сотувчи билан боғланиб ҳолатни текширади ва ечим таклиф қилади.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Мой заказ задерживается более 20-30 дней, что делать?</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Приносим извинения за задержку. Отправьте DG номер(а) заказа — наши специалисты свяжутся с продавцом, проверят статус и предложат решение.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>My order is delayed more than 20-30 days, what should I do?</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>We apologize for the delay. Send the DG number(s) of the order — our specialists will contact the seller, check the status and offer a solution.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>我的订单延误超过20-30天，怎么办？</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>对于延误我们深表歉意。请发送订单DG号，我们的专家会联系卖家检查状态并提供解决方案。</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -655,8 +943,48 @@
           <t>Ha, ayniqsa oktyabr oyidagi bayramlar va boshqa yirik dam olish kunlarida sotuvchilar va logistika sekinroq ishlaydi.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Хитой байрамларида етказиш кечикадими?</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, айниқса октябр ойидаги байрамлар ва бошқа йирик дам олиш кунларида сотувчилар ва логистика секинроқ ишлайди.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Задерживается ли доставка в китайские праздники?</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Да, особенно во время октябрьских праздников и других крупных выходных продавцы и логистика работают медленнее.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Does delivery get delayed during Chinese holidays?</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Yes, especially during October holidays and other major holidays, sellers and logistics work slower.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>中国节日期间会延误配送吗？</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>是的，尤其是十月假期和其他重大节假日期间，卖家和物流速度会变慢。</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -682,8 +1010,48 @@
           <t>Ko'pincha pochta orqali yuborilganda shunday ko'rsatiladi. Eng yaqin pochta bo'limi yoki EMU punktini tekshiring. Buyurtma raqamini yuborsangiz aniqlashtiramiz.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>"Мижозга топширилди" ҳолати чиқди, лекин мен олдим.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Кўпинча почта орқали юборилганда шундай кўрсатилади. Энг яқин почта бўлими ёки EMU пунктини текширинг. Буюртма рақамини юборсангиз аниқлаштирамиз.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Статус "Доставлено клиенту" появился, но я не получал.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Часто так отображается при отправке через почту. Проверьте ближайшее отделение почты или пункт EMU. Отправьте номер заказа, мы уточним.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>"Delivered to customer" status appeared, but I didn't receive it.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>This often happens when sent via post. Check the nearest post office or EMU pickup point. Send your order number and we will clarify.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>显示“已交付给客户”状态，但我没有收到。</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>通过邮局发送时经常这样显示。请检查最近的邮局或EMU自提点。发送订单号，我们会帮您确认。</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -709,8 +1077,48 @@
           <t>Punktgacha yetkazish bepul. Og'ir buyurtmalar uchun qo'shimcha kargo haqini mutaxassis aniq hisoblab beradi.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Карго (оғир юк) нархи қанча?</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Пунктгача етказиш бепул. Оғир буюртмалар учун қўшимча карго ҳақини мутахассис аниқ ҳисоблаб беради.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Сколько стоит карго (тяжёлый груз)?</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Доставка до пункта бесплатная. Для тяжёлых заказов дополнительную стоимость карго точно рассчитает специалист.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>What is the cargo (heavy load) price?</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Delivery to the pickup point is free. For heavy orders, the specialist will calculate the additional cargo fee exactly.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>货物（重货）价格是多少？</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>送到自提点免费。对于重货订单，专家会精确计算额外的货物费用。</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -736,8 +1144,48 @@
           <t>Ilovadagi "Buyurtmalarim" bo'limini oching yoki bizga DG raqami yoki tracking raqam (YT, JT, 78...) ni yuboring.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма ҳолатини қандай кузатаман?</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Иловадаги "Буюртмаларим" бўлимини очинг ёки бизга DG рақами ёки tracking рақам (YT, JT, 78...) ни юборинг.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Как отслеживать статус заказа?</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Откройте раздел "Мои заказы" в приложении или отправьте нам DG номер или трекинг-номер (YT, JT, 78...).</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>How can I track my order status?</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Open the "My Orders" section in the app or send us the DG number or tracking number (YT, JT, 78...).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>如何跟踪订单状态？</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>打开应用中的“我的订单”部分，或发送DG号或跟踪号（YT、JT、78...）。</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -763,8 +1211,48 @@
           <t>Barcha DG yoki tracking raqamlarini yozib yuboring, hammasini tekshirib javob beramiz.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Бир нечта буюртмам бор, ҳаммасини текшириб берсангиз?</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Барча DG ёки tracking рақамларини ёзиб юборинг, ҳаммасини текшириб жавоб берамиз.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>У меня несколько заказов, можете проверить все?</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Напишите все DG или трекинг-номера, мы проверим и ответим по каждому.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>I have multiple orders, can you check all of them?</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Write all DG or tracking numbers, we will check and reply for each.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>我有多个订单，可以帮我全部检查吗？</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>请写下所有DG号或跟踪号，我们会逐一检查并回复。</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -790,8 +1278,48 @@
           <t>Buyurtma raqamini yuboring. Mutaxassislarimiz sotuvchi bilan bog'lanib holatni aniqlaydi.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Статус қотиб қолган, ҳеч қандай ўзгариш йўқ.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма рақамини юборинг. Мутахассисларимиз сотувчи билан боғланиб ҳолатни аниқлайди.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Статус завис, никаких изменений нет.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте номер заказа. Наши специалисты свяжутся с продавцом и уточнят статус.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>The status is stuck, there are no changes.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Send your order number. Our specialists will contact the seller and clarify the status.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>状态卡住了，没有任何变化。</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单号。我们的专家会联系卖家确认状态。</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -817,8 +1345,48 @@
           <t>Agar buyurtma hali jo'natilmagan bo'lsa, bekor qilish mumkin. Raqamni yuboring.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани бекор қилмоқчиман.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Агар буюртма ҳали жўнатилмаган бўлса, бекор қилиш мумкин. Рақамни юборинг.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Хочу отменить заказ.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Если заказ ещё не отправлен, его можно отменить. Отправьте номер.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>I want to cancel the order.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>If the order has not been shipped yet, it can be cancelled. Send the number.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>我想取消订单。</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>如果订单尚未发货，可以取消。请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -844,8 +1412,48 @@
           <t>Ilovadagi "Buyurtmalarim" bo'limida har bir buyurtma uchun DG raqami ko'rsatilgan.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма рақамини қаердан топаман?</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Иловадаги "Буюртмаларим" бўлимида ҳар бир буюртма учун DG рақами кўрсатилган.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Где найти номер заказа?</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>В разделе "Мои заказы" в приложении для каждого заказа указан DG номер.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Where can I find the order number?</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>In the "My Orders" section of the app, the DG number is shown for each order.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>在哪里找到订单号？</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>在应用的“我的订单”部分，每个订单都会显示DG号。</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -871,8 +1479,48 @@
           <t>Uzr so'raymiz. Buyurtma DG raqami, xitoycha stiker rasmi va kelgan tovar rasmini yuboring. Almashtirish yoki qaytarishni hal qilamiz.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Нотоғри маҳсулот келди.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Узр сўраймиз. Буюртма DG рақами, хитойча стикер расми ва келган товар расмини юборинг. Алмаштириш ёки қайтаришни ҳал қиламиз.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Пришёл неправильный товар.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Приносим извинения. Отправьте DG номер заказа, фото китайского стикера и фото полученного товара. Мы решим вопрос с заменой или возвратом.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Wrong product arrived.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>We apologize. Send the order DG number, photo of the Chinese sticker and photo of the received product. We will resolve the replacement or return.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>收到了错误的产品。</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>我们深表歉意。请发送订单DG号、中国贴纸照片和收到产品的照片。我们会处理更换或退货。</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -898,8 +1546,48 @@
           <t>Foto va video bilan birga DG raqamini yuboring. Mutaxassislarimiz almashtirish yoki pulni qaytarish choralarini ko'radi.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Брак (сифатсиз) маҳсулот келди.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Фото ва видео билан бирга DG рақамини юборинг. Мутахассисларимиз алмаштириш ёки пулни қайтариш чораларини кўради.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Пришёл бракованный (некачественный) товар.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте DG номер вместе с фото и видео. Наши специалисты примут меры по замене или возврату денег.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Defective (low quality) product arrived.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Send the DG number along with photos and videos. Our specialists will take measures for replacement or refund.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>收到了残次品（质量差的产品）。</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>请发送DG号以及照片和视频。我们的专家会采取更换或退款措施。</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -925,8 +1613,48 @@
           <t>Ha. Kelmay qolgan tovar raqamlarini va yangi tanlagan tovarlarni yozing. Narx farqi bo'lsa balans orqali hal qilinadi.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Келмай қолган товарларни бошқасига алмаштирса бўладими?</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа. Келмай қолган товар рақамларини ва янги танлаган товарларни ёзинг. Нарх фарқи бўлса баланс орқали ҳал қилинади.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли заменить недостающие товары на другие?</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Да. Напишите номера недостающих товаров и новые выбранные товары. Разница в цене будет урегулирована через баланс.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Can I replace the missing items with others?</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Yes. Write the numbers of the missing items and the new items you have chosen. If there is a price difference, it will be resolved through the balance.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>可以把没收到的商品换成其他吗？</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>可以。请写下缺失商品的编号和新选择的商品。价格差额将通过余额解决。</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -952,8 +1680,48 @@
           <t>Ha, brak yoki noto'g'ri tovar bo'lsa almashtirish yoki pulni qaytarish mumkin. Tegishli rasmlar va DG raqamini yuboring.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулотни қайтариш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, брак ёки нотоғри товар бўлса алмаштириш ёки пулни қайтариш мумкин. Тегишли расмлар ва DG рақамини юборинг.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли вернуть товар?</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Да, если товар бракованный или неправильный, возможна замена или возврат денег. Отправьте соответствующие фото и DG номер.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Can I return the product?</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Yes, if the product is defective or incorrect, replacement or refund is possible. Send the relevant photos and DG number.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>可以退货吗？</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>可以，如果是残次品或错误商品，可以更换或退款。请发送相关照片和DG号。</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -979,8 +1747,48 @@
           <t>Pul balansingizga tushgan bo'lishi mumkin. Ilovadagi balansni tekshiring.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов қилдим, лекин буюртма тасдиқланмади.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Пул балансингизга тушган бўлиши мумкин. Иловадаги балансни текширинг.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Я оплатил, но заказ не подтверждён.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Деньги могли поступить на ваш баланс. Проверьте баланс в приложении.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>I made a payment, but the order was not confirmed.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>The money may have been credited to your balance. Check the balance in the app.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>我已付款，但订单未确认。</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>款项可能已进入您的余额。请检查应用中的余额。</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1006,8 +1814,48 @@
           <t>Ortig'ini balansga qaytaramiz. Buyurtma raqamini yuboring.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Икки марта тўлов чиқди.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Ортиғини балансга қайтарамиз. Буюртма рақамини юборинг.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Произошла двойная оплата.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Излишек мы вернём на баланс. Отправьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Double payment was charged.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>We will refund the excess to your balance. Send your order number.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>出现了重复付款。</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>多付的金额我们会退回到余额。请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1033,8 +1881,48 @@
           <t>Bekor qilingan yoki muammoli buyurtmalar bo'yicha odatda 48 soat ichida balansga qaytariladi.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Пулни қайтариш қанча вақт олади?</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Бекор қилинган ёки муаммоли буюртмалар бўйича одатда 48 соат ичида балансга қайтарилади.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает возврат денег?</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>По отменённым или проблемным заказам деньги обычно возвращаются на баланс в течение 48 часов.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>How long does a refund take?</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>For cancelled or problematic orders, money is usually returned to the balance within 48 hours.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>退款需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>对于取消或有问题的订单，款项通常在48小时内退回到余额。</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1060,8 +1948,48 @@
           <t>Hozircha faqat balans orqali boshqa buyurtmalarga ishlatish mumkin.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Балансдаги пулни картага қайтариб бўладими?</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Ҳозирча фақат баланс орқали бошқа буюртмаларга ишлатиш мумкин.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли вывести деньги с баланса на карту?</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>На данный момент средства с баланса можно использовать только для других заказов.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Can I transfer the balance money back to my card?</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Currently, the balance can only be used for other orders.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>余额的钱可以退回到银行卡吗？</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>目前余额只能用于其他订单。</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1087,8 +2015,48 @@
           <t>B2B orqali har bir kg uchun kargo to'lovi bilan narx 20% arzon bo'ladi. Dona bo'lsa ham buyurtma berish mumkin. Pasport ma'lumotlari yetarli.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>B2B (улгуржи) бўлими қандай ишлайди?</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>B2B орқали ҳар бир кг учун карго тўлови билан нарх 20% арзон бўлади. Дона бўлса ҳам буюртма бериш мумкин. Паспорт маълумотлари етарли.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Как работает раздел B2B (опт)?</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Через B2B цена на 20% дешевле с оплатой карго за каждый кг. Можно заказывать и поштучно. Достаточно паспортных данных.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>How does the B2B (wholesale) section work?</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Through B2B, the price is 20% cheaper with cargo payment per kg. You can also order by piece. Passport data is sufficient.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>B2B（批发）部分如何运作？</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>通过B2B，每公斤货物费用后价格便宜20%。也可以按件订购。只需护照信息即可。</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1114,8 +2082,48 @@
           <t>Yo'q, B2B da har kg uchun alohida to'lov mavjud.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>B2B да ҳам 7 кг гача бепул етказиб бериш борми?</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Йўқ, B2B да ҳар кг учун алоҳида тўлов мавжуд.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>В B2B тоже есть бесплатная доставка до 7 кг?</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Нет, в B2B за каждый кг взимается отдельная плата.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Is there free delivery up to 7 kg in B2B as well?</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>No, in B2B there is a separate payment for each kg.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>B2B也有7公斤内免费配送吗？</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>没有，B2B中每公斤都需要单独付费。</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1141,8 +2149,48 @@
           <t>Ilovani oxirgi versiyaga yangilab ko'ring. Muammo davom etsa skrinshot yuboring.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Иловада тўлов ўтмаяпти.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Иловани охирги версияга янглаб кўринг. Муаммо давом этса скриншот юборинг.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>В приложении не проходит оплата.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Попробуйте обновить приложение до последней версии. Если проблема persists, отправьте скриншот.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Payment is not going through in the app.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Try updating the app to the latest version. If the problem continues, send a screenshot.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>应用中无法完成支付。</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>请尝试将应用更新到最新版本。如果问题仍然存在，请发送截图。</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1168,8 +2216,48 @@
           <t>Ilovadagi shaxsiy ma'lumotlar bo'limida o'zgartirishingiz mumkin. Muammo bo'lsa yordam so'rang.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Телефон рақамини ўзгартириш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Иловадаги шахсий маълумотлар бўлимида ўзгартиришингиз мумкин. Муаммо бўлса ёрдам сўранг.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли изменить номер телефона?</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Вы можете изменить его в разделе «Личные данные» в приложении. Если возникнут проблемы, обратитесь за помощью.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Can I change my phone number?</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>You can change it in the Personal Information section of the app. If you have any issues, please ask for help.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>可以更改电话号码吗？</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>您可以在应用中的“个人信息”部分进行更改。如果遇到问题，请寻求帮助。</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1195,8 +2283,48 @@
           <t>Agar tovar brak yoki noto'g'ri bo'lsa — ha. Oddiy "yoqmasa" holatida qaytarish cheklangan.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот сифати ёқмаса пулни қайтарасизми?</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Агар товар брак ёки нотоғри бўлса — ҳа. Оддий "ёқмаса" ҳолатида қайтариш чекланган.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Если качество товара не понравилось, вернёте деньги?</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Если товар бракованный или неправильный — да. В случае обычного «не понравилось» возврат ограничен.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>If I don't like the product quality, will you refund?</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>If the product is defective or incorrect — yes. For regular "don't like it" cases, refund is limited.</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>如果产品质量不喜欢，可以退款吗？</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>如果是残次品或错误商品——可以。普通“不喜欢”的情况退款有限制。</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1222,8 +2350,48 @@
           <t>Yetkazishdan 30-60 daqiqa oldin SMS yoki qo'ng'iroq qilinadi.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Курьер қачон телефон қилади?</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Етказишдан 30-60 дақиқа олдин SMS ёки қўнғироқ қилинади.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Когда курьер позвонит?</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>За 30-60 минут до доставки придёт SMS или звонок.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>When will the courier call?</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>An SMS or call will be made 30-60 minutes before delivery.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>快递员什么时候打电话？</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>配送前30-60分钟会发送短信或致电。</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1249,8 +2417,48 @@
           <t>24 soat ichida foto/video bilan operatorga yozing — almashtiramiz yoki pulni qaytaramiz.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот бузилган ёки нотоғри келди, нима қилиш керак?</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>24 соат ичида фото/видео билан операторга ёзинг — алмаштирамиз ёки пулни қайтарамиз.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Товар пришёл повреждённым или неправильным, что делать?</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Напишите оператору в течение 24 часов с фото/видео — мы заменим или вернём деньги.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>The product arrived damaged or incorrect, what should I do?</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Write to the operator within 24 hours with photos/videos — we will replace or refund.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>产品损坏或错误送达，怎么办？</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>请在24小时内带照片/视频联系客服——我们会更换或退款。</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1276,8 +2484,48 @@
           <t>Buyurtma raqamini yuboring, mutaxassislarimiz izlab topishga harakat qiladi.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма йўқолиб қолди шекилли.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма рақамини юборинг, мутахассисларимиз излаб топишга ҳаракат қилади.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Похоже, заказ потерялся.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте номер заказа, наши специалисты постараются найти его.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>It seems the order is lost.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Send the order number, our specialists will try to find it.</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>订单好像丢失了。</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单号，我们的专家会努力查找。</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1303,8 +2551,48 @@
           <t>Odatda 1-3 ish kuni ichida yetkaziladi.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Тошкент ичида етказиб бериш қанча вақт олади?</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Одатда 1-3 иш куни ичида етказилади.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает доставка внутри Ташкента?</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Обычно доставка осуществляется в течение 1-3 рабочих дней.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>How long does delivery take within Tashkent?</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Usually delivered within 1-3 business days.</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>塔什干市内配送需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>通常在1-3个工作日内送达。</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1330,8 +2618,48 @@
           <t>Toshkentga kelgandan keyin pochta orqali 3-7 ish kuni.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Вилоятларга етказиш муддати қанча?</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Тошкентга келгандан кейин почта орқали 3-7 иш куни.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает доставка в регионы?</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>После прибытия в Ташкент — 3-7 рабочих дней через почту.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>How long does delivery to regions take?</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>After arriving in Tashkent, 3-7 business days via post.</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>配送到各地区需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>到达塔什干后，通过邮政需要3-7个工作日。</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1357,8 +2685,48 @@
           <t>Ilovada "Buyurtmalarim" bo'limida yoki tracking raqam orqali.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани қандай кузатиш мумкин?</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Иловада "Буюртмаларим" бўлимида ёки tracking рақам орқали.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Как отслеживать заказ?</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>В разделе «Мои заказы» в приложении или по трекинг-номеру.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>How can I track the order?</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>In the "My Orders" section of the app or via tracking number.</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>如何跟踪订单？</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>在应用“我的订单”部分或通过跟踪号。</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1384,8 +2752,48 @@
           <t>Bank kartasi, Click, Payme va balans orqali.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Қандай тўлов усуллари мавжуд?</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Банк картаси, Click, Payme ва баланс орқали.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Какие способы оплаты доступны?</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Банковская карта, Click, Payme и через баланс.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>What payment methods are available?</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Bank card, Click, Payme, and through balance.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>有哪些支付方式？</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>银行卡、Click、Payme 和余额支付。</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1411,8 +2819,48 @@
           <t>Brak holatida 14 kun ichida qaytarish mumkin.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Қайтариш муддати қанча?</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Брак ҳолатида 14 кун ичида қайтариш мумкин.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Какой срок возврата?</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>В случае брака возврат возможен в течение 14 дней.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>What is the return period?</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>In case of defect, return is possible within 14 days.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>退货期限是多久？</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>残次品情况下可在14天内退货。</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1438,8 +2886,48 @@
           <t>Kelmay qolgan tovar raqamlarini yozing, almashtiramiz.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Бир хил буюртмада бир нечта товар келмади.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Келмай қолган товар рақамларини ёзинг, алмаштирамиз.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>В одном заказе не пришло несколько товаров.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Напишите номера недостающих товаров, мы их заменим.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Some items are missing from the same order.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Write the numbers of the missing items, we will replace them.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>同一订单中缺少多个商品。</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>请写下缺失商品的编号，我们会进行更换。</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1465,8 +2953,48 @@
           <t>Pasport ma'lumotlari yetarli, qo'shimcha hujjat talab qilinmaydi.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>B2B га рўйхатдан ўтиш учун нима керак?</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт маълумотлари етарли, қўшимча ҳужжат талаб қилинмайди.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Что нужно для регистрации в B2B?</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Достаточно паспортных данных, дополнительных документов не требуется.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>What is needed to register for B2B?</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Passport data is sufficient, no additional documents are required.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>注册B2B需要什么？</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>只需护照信息，无需额外文件。</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1492,8 +3020,48 @@
           <t>Ilovani yangilab, cache ni tozalab ko'ring.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Балансдаги пул кўринмаяпти.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Иловани янглаб, cache ни тозалаб кўринг.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Деньги на балансе не отображаются.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Обновите приложение и очистите кэш.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>The money in the balance is not showing.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Update the app and clear the cache.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>余额中的钱不显示。</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>请更新应用并清除缓存。</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1519,8 +3087,48 @@
           <t>Ushbu chat orqali yozishingiz mumkin.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Яна саволим бўлса қаерга мурожаат қиламан?</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Ушбу чат орқали ёзишингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Если у меня возникнут ещё вопросы, куда обращаться?</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Вы можете написать в этот чат.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>If I have more questions, where should I contact?</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>You can write through this chat.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>如果我还有其他问题，应该联系哪里？</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>您可以通过此聊天联系我们。</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1546,8 +3154,48 @@
           <t>Buyurtma holatida yoki bizga yozsangiz aniq manzil beramiz.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Пункт манзилини қаердан биламан?</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма ҳолатида ёки бизга ёзсангиз аниқ манзил берамиз.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Где узнать адрес пункта?</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>В статусе заказа или напишите нам — мы укажем точный адрес.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Where can I find the pickup point address?</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>In the order status or write to us — we will give the exact address.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>在哪里知道自提点地址？</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>在订单状态中或联系我们——我们会提供确切地址。</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1573,8 +3221,48 @@
           <t>Toshkentda tezroq, viloyatlarda pochta orqali.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Етказиб беришда фарқ борми?</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Тошкентда тезроқ, вилоятларда почта орқали.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Есть ли разница в доставке?</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>В Ташкенте быстрее, в регионах — через почту.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Is there a difference in delivery?</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Faster in Tashkent, in regions — via post.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>配送有区别吗？</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>塔什干更快，其他地区通过邮政。</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1600,8 +3288,48 @@
           <t>Raqamni yuboring, tekshirib beramiz.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма ҳолати "Номаълум" чиқяпти.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Рақамни юборинг, текшириб берамиз.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Статус заказа показывает "Неизвестно".</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте номер, мы проверим.</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>The order status shows "Unknown".</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Send the number, we will check it.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>订单状态显示“未知”。</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单号，我们会帮您检查。</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1627,8 +3355,48 @@
           <t>Bir necha daqiqa kutib yana tekshiring.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Тўловдан кейин баланс янгиланмаяпти.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Бир неча дақиқа кутиб яна текширинг.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>После оплаты баланс не обновляется.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Подождите несколько минут и проверьте снова.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>The balance is not updating after payment.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Wait a few minutes and check again.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>付款后余额没有更新。</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>请等待几分钟后再次检查。</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1654,8 +3422,48 @@
           <t>Rasmlar bilan DG raqamini yuboring.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот ранги нотоғри келди.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Расмлар билан DG рақамини юборинг.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Пришёл товар неправильного цвета.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте фото и DG номер.</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>The product came in the wrong color.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Send photos along with the DG number.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>产品颜色错误。</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>请发送照片和DG号。</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1681,8 +3489,48 @@
           <t>48 soat ichida balansga tushadi.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Қайтарилган пул қачон келади?</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>48 соат ичида балансга тушади.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Когда вернутся деньги?</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Деньги поступят на баланс в течение 48 часов.</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>When will the refunded money arrive?</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>It will be credited to the balance within 48 hours.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>退款什么时候到账？</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>退款将在48小时内进入余额。</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1708,8 +3556,48 @@
           <t>Yo'q, istalgan miqdorda buyurtma berish mumkin.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>B2B да минимал буюртма миқдори борми?</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Йўқ, исталган миқдорда буюртма бериш мумкин.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Есть ли минимальный объём заказа в B2B?</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Нет, можно заказывать в любом количестве.</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Is there a minimum order quantity in B2B?</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>No, you can place an order in any quantity.</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>B2B有最小订单量要求吗？</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>没有，可以任意数量下单。</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1735,8 +3623,48 @@
           <t>Ilovani yangilang yoki cache ni tozalang.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Илова хато бераяпти.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Иловани янгиланг ёки cache ни тозаланг.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Приложение выдаёт ошибку.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Обновите приложение или очистите кэш.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>The app is giving an error.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Update the app or clear the cache.</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>应用出错。</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>请更新应用或清除缓存。</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1762,8 +3690,48 @@
           <t>Ushbu chat orqali yozing, mutaxassis aloqaga chiqadi.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Оператор билан гаплашмоқчиман.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Ушбу чат орқали ёзинг, мутахассис алоқага чиқади.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Хочу поговорить с оператором.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Напишите в этот чат, специалист свяжется с вами.</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>I want to talk to an operator.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Write in this chat, a specialist will contact you.</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>我想和客服通话。</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>请在此聊天中留言，客服会与您联系。</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1789,8 +3757,48 @@
           <t>Pochtada olganingizda to'lov amalga oshiriladi.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Почта орқали етказиш қанча туради?</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Почтада олганингизда тўлов амалга оширилади.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Сколько стоит доставка через почту?</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Оплата производится при получении на почте.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>How much does delivery via post cost?</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Payment is made upon receipt at the post office.</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>通过邮局配送需要多少钱？</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>在邮局取件时支付费用。</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1816,8 +3824,48 @@
           <t>Ilovani yangilab ko'ring.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Эски буюртмаларимни кўра олмаяпман.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Иловани янглаб кўринг.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Не могу увидеть старые заказы.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Попробуйте обновить приложение.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>I can't see my old orders.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Try updating the app.</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>看不到以前的订单。</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>请尝试更新应用。</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1843,8 +3891,48 @@
           <t>Toshkentga kelgandan keyin 3-5 kun ichida.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма Фарғонага қачон етади?</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Тошкентга келгандан кейин 3-5 кун ичида.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Когда заказ прибудет в Фергану?</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>После прибытия в Ташкент — в течение 3-5 дней.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>When will the order arrive in Fergana?</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Within 3-5 days after arriving in Tashkent.</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>订单什么时候到费尔干纳？</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>到达塔什干后3-5天内送达。</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1870,8 +3958,48 @@
           <t>Rasmlar va DG raqamini yuboring.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот сифати паст чиқди.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Расмлар ва DG рақамини юборинг.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Качество товара оказалось низким.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте фото и DG номер.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>The product quality turned out to be low.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Send photos and the DG number.</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>产品质量很差。</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>请发送照片和DG号。</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1897,8 +4025,48 @@
           <t>Boshqa kartani sinab ko'ring yoki balansdan foydalaning.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Карта орқали тўлов муваффақиятсиз.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Бошқа картани синаб кўринг ёки балансдан фойдаланинг.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Оплата картой не прошла.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Попробуйте другую карту или оплатите с баланса.</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Payment via card was unsuccessful.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Try another card or use your balance.</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>银行卡支付失败。</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>请尝试其他银行卡或使用余额支付。</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1924,8 +4092,48 @@
           <t>Sotuvchi tomonidan bekor qilingan bo'lishi mumkin.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма бекор бўлди, нега?</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Сотувчи томонидан бекор қилинган бўлиши мумкин.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Заказ был отменён, почему?</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Возможно, отменён продавцом.</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>The order was cancelled, why?</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>It may have been cancelled by the seller.</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>订单被取消了，为什么？</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>可能是卖家取消的。</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1951,8 +4159,48 @@
           <t>Foto va DG raqam bilan yozing.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Брак товарни қандай қайтараман?</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Фото ва DG рақам билан ёзинг.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Как вернуть бракованный товар?</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Напишите с фото и DG номером.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>How do I return a defective item?</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Write with photos and the DG number.</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>如何退回残次品？</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>请带照片和DG号留言。</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1978,8 +4226,48 @@
           <t>Odatda 20% gacha chegirma mavjud.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>B2B нархлари қанча арзон?</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Одатда 20% гача чегирма мавжуд.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Насколько дешевле цены в B2B?</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Обычно действует скидка до 20%.</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>How much cheaper are B2B prices?</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Usually there is a discount of up to 20%.</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>B2B价格便宜多少？</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>通常有高达20%的折扣。</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2005,8 +4293,48 @@
           <t>Ushbu chat orqali yozish eng tez yo'l.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий билан боғланиш учун телефон рақами?</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Ушбу чат орқали ёзиш энг тез йўл.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Какой номер телефона для связи с Sahiy?</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Самый быстрый способ — написать в этот чат.</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>What is the phone number to contact Sahiy?</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>The fastest way is to write through this chat.</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>联系Sahiy的电话号码是多少？</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>最快的方式是通过此聊天留言。</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2032,8 +4360,48 @@
           <t>Punktgacha — ha.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Етказиб бериш бепулми?</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Пунктгача — ҳа.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Доставка бесплатная?</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>До пункта выдачи — да.</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Is delivery free?</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>To the pickup point — yes.</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>配送是免费的吗？</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>送到自提点——是的。</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2059,8 +4427,48 @@
           <t>Ha, muammo hal qilinganidan keyin.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани қайта юбориш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, муаммо ҳал қилинганидан кейин.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли отправить заказ заново?</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Да, после решения проблемы.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Can the order be resent?</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Yes, after the issue is resolved.</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>可以重新发送订单吗？</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>是的，问题解决后可以。</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2086,8 +4494,48 @@
           <t>Raqam to'g'riligini tekshiring.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SMS келмаяпти.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Рақам тўғрилигини текширинг.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>SMS не приходит.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Проверьте правильность номера.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>SMS is not coming.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Check if the number is correct.</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>收不到短信。</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>请检查号码是否正确。</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2113,8 +4561,48 @@
           <t>Toshkentdan keyin 4-7 kun.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Андижонга етказиш қанча вақт олади?</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Тошкентдан кейин 4-7 кун.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает доставка в Андижан?</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>После прибытия в Ташкент — 4-7 дней.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>How long does delivery to Andijan take?</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Within 4-7 days after arriving in Tashkent.</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>配送到安集延需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>到达塔什干后4-7天。</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2140,8 +4628,48 @@
           <t>Rasmlar bilan murojaat qiling.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Товар оригинал эмас.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Расмлар билан мурожаат қилинг.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Товар не оригинальный.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Обратитесь с фотографиями.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>The item is not original.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Contact us with photos.</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>商品不是正品。</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>请带照片联系我们。</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2167,8 +4695,48 @@
           <t>To'lov skrinshotini yuboring.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Балансга пул тушмаяпти.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов скриншотини юборинг.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Деньги не поступают на баланс.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте скриншот оплаты.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Money is not credited to the balance.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Send a screenshot of the payment.</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>余额没有到账。</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>请发送支付截图。</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2194,8 +4762,48 @@
           <t>Raqam yuboring.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма статуси ўзгармаяпти.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Рақамни юборинг.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Статус заказа не меняется.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>The order status is not changing.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Send the order number.</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>订单状态没有变化。</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2221,8 +4829,48 @@
           <t>Brak bo'lsa — mumkin.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>14 кундан ошган товарни қайтариш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Брак бўлса — мумкин.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли вернуть товар после 14 дней?</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Если товар бракованный — можно.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Can I return an item after 14 days?</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>If it is defective — yes.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>超过14天的商品可以退货吗？</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>如果是残次品——可以。</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2248,8 +4896,48 @@
           <t>Yo'q, pasport yetarli.</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>B2B да ҳужжат керакми?</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Йўқ, паспорт етарли.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Нужны ли документы для B2B?</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Нет, достаточно паспортных данных.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Are documents required for B2B?</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>No, passport data is sufficient.</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>B2B需要文件吗？</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>不需要，只需护照信息即可。</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2275,8 +4963,48 @@
           <t>Bu yerda yozing, tezroq yordam beramiz.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Оператор жавоб бермаяпти.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Бу ерда ёзинг, тезроқ ёрдам берамиз.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Оператор не отвечает.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Напишите здесь, мы поможем быстрее.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>The operator is not responding.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Write here, we will help you faster.</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>客服没有回复。</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>请在这里留言，我们会更快地帮助您。</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2302,8 +5030,48 @@
           <t>Pochta orqali 3-6 kun.</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Самарқандга қачон етади?</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Почта орқали 3-6 кун.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Когда прибудет в Самарканд?</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Через почту — 3-6 дней.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>When will it arrive in Samarkand?</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Via post — 3-6 days.</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>什么时候到撒马尔罕？</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>通过邮政需要3-6天。</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2329,8 +5097,48 @@
           <t>Foto bilan yozing.</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Ўлчами мос келмади.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Фото билан ёзинг.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Размер не подошёл.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Напишите с фото.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>The size didn't fit.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Write with a photo.</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尺寸不合适。</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>请带照片留言。</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2356,8 +5164,48 @@
           <t>48 soatdan 3 kungacha.</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов қайтариш жараёни қанча давом этади?</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>48 соатдан 3 кунгача.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает процесс возврата денег?</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>От 48 часов до 3 дней.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>How long does the refund process take?</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>From 48 hours to 3 days.</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>退款流程需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>48小时到3天。</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2383,8 +5231,48 @@
           <t>Raqam yuboring.</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма пунктга келди, лекин хабар йўқ.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Рақамни юборинг.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Заказ прибыл в пункт, но нет уведомления.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>The order has arrived at the pickup point, but there is no notification.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Send the order number.</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>订单已到自提点，但没有通知。</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2410,8 +5298,48 @@
           <t>Buyurtma berganingizdan keyin odatda 12–15 kun ichida yetib keladi. Viloyatlarda 20 kungacha cho'zilishi mumkin.</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Етказиб бериш қанча вақт олади?</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма берганингиздан кейин одатда 12–15 кун ичида етиб келади. Вилоятларда 20 кунгача чўзилиши мумкин.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает доставка?</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>После оформления заказа обычно доставка занимает 12–15 дней. В регионах может занять до 20 дней.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>How long does delivery take?</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>After placing your order, it usually arrives within 12–15 days. In regions, it may take up to 20 days.</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>配送需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>下单后通常12-15天内到达。地区可能需要最多20天。</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2437,8 +5365,48 @@
           <t>Buyurtma jo'natilmaguncha profil orqali yoki operatorga murojaat qilib bekor qilishingiz mumkin.</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани қандай бекор қиламан?</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма жўнатилмагунча профил орқали ёки операторга мурожаат қилиб бекор қилишингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Как отменить заказ?</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Пока заказ не отправлен, вы можете отменить его через профиль или обратившись к оператору.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>How do I cancel an order?</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>You can cancel the order through your profile or by contacting the operator before it is shipped.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>如何取消订单？</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>在订单发货前，您可以通过个人资料或联系客服取消。</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2464,8 +5432,48 @@
           <t>Naqd pul, bank kartasi va Click/Payme orqali to'lash mumkin.</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Қандай тўлов усуллари мавжуд?</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Нақд пул, банк картаси ва Click/Payme орқали тўлаш мумкин.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Какие способы оплаты доступны?</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Наличные, банковская карта, а также Click и Payme.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>What payment methods are available?</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Cash, bank card, and via Click/Payme.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>有哪些支付方式？</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>现金、银行卡以及Click/Payme支付。</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2491,8 +5499,48 @@
           <t>Ha, 14 kun ichida sifatli holatda qaytarish mumkin. Chek va qadoq talab qilinadi.</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулотни қайтариш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, 14 кун ичида сифатли ҳолатда қайтариш мумкин. Чек ва қадоқ талаб қилинади.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли вернуть товар?</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Да, в течение 14 дней в надлежащем качестве. Требуется чек и упаковка.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Can I return the product?</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Yes, within 14 days if the product is in good condition. Receipt and packaging are required.</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>可以退货吗？</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>可以，在14天内且商品完好。需要发票和包装。</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2518,8 +5566,48 @@
           <t>24 soat ichida foto/video bilan operatorga yozing — almashtiramiz yoki pulni qaytaramiz.</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот бузилган ёки нотоғри келди, нима қилиш керак?</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>24 соат ичида фото/видео билан операторга ёзинг — алмаштирамиз ёки пулни қайтарамиз.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Товар пришёл повреждённым или неправильным, что делать?</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Напишите оператору в течение 24 часов с фото/видео — мы заменим или вернём деньги.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>The product arrived damaged or incorrect, what should I do?</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Write to the operator within 24 hours with photo/video — we will replace or refund.</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>产品损坏或送错，怎么办？</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>请在24小时内带照片/视频联系客服——我们会更换或退款。</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2545,8 +5633,48 @@
           <t>Yetkazishdan 30-60 daqiqa oldin SMS yoki qo'ng'iroq qilinadi.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Курьер қачон телефон қилади?</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Етказишдан 30-60 дақиқа олдин SMS ёки қўнғироқ қилинади.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Когда курьер позвонит?</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>За 30-60 минут до доставки придёт SMS или звонок.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>When will the courier call?</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SMS or call will be made 30-60 minutes before delivery.</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>快递员什么时候打电话？</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>配送前30-60分钟会发送短信或打电话。</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2572,8 +5700,48 @@
           <t>Ushbu chat orqali murojaat qiling.</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Ёрдам маркази қаерда?</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Ушбу чат орқали мурожаат қилинг.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Где центр помощи?</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Обратитесь через этот чат.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Where is the help center?</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Contact us through this chat.</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>帮助中心在哪里？</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>请通过此聊天联系我们。</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2599,8 +5767,48 @@
           <t>Ilovadagi "Buyurtmalarim" bo'limida.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Эски буюртмалар тарихини қандай кўраман?</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Иловадаги "Буюртмаларим" бўлимида.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Как посмотреть историю старых заказов?</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>В разделе «Мои заказы» в приложении.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>How can I see the history of old orders?</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>In the "My Orders" section of the app.</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>如何查看旧订单历史？</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>在应用中的“我的订单”部分查看。</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2626,8 +5834,48 @@
           <t>DG raqami va rasmlarni yuboring.</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Товар бошқа мижозникига ўхшаб келди.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>DG рақами ва расмларни юборинг.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Товар пришёл похожим на заказ другого клиента.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте DG номер и фото.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>The item looks like it belongs to another customer.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Send the DG number and photos.</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>商品看起来像是别人的。</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>请发送DG号和照片。</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2653,8 +5901,48 @@
           <t>Boshqa usulni sinab ko'ring.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Click орқали тўлов қилишда муаммо.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Бошқа усулни синаб кўринг.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Проблема с оплатой через Click.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Попробуйте другой способ оплаты.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Problem with payment via Click.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Try another payment method.</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>通过Click支付时出现问题。</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>请尝试其他支付方式。</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2680,8 +5968,48 @@
           <t>B2B bo'limiga o'ting.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Улгуржи нархларни қаердан кўраман?</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>B2B бўлимига ўтинг.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Где посмотреть оптовые цены?</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Перейдите в раздел B2B.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Where can I see wholesale prices?</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Go to the B2B section.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>在哪里查看批发价格？</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>请进入B2B部分。</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2707,8 +6035,48 @@
           <t>3-6 ish kuni.</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Наманганга етказиш муддати?</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>3-6 иш куни.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Срок доставки в Наманган?</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>3-6 рабочих дней.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>What is the delivery time to Namangan?</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>3-6 business days.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>配送到纳曼干需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3-6个工作日。</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2734,8 +6102,48 @@
           <t>Balansdan yangi buyurtma qiling.</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Пул қайтарилгандан кейин нима қиламан?</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Балансдан янги буюртма қилинг.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Что делать после возврата денег?</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Сделайте новый заказ с баланса.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>What should I do after the money is refunded?</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Place a new order from your balance.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>退款到账后怎么办？</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>请使用余额下新订单。</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2761,8 +6169,48 @@
           <t>Keshni tozalang va yangilang.</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Илова секин ишлаяпти.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Кешни тозаланг ва янгиланг.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Приложение работает медленно.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Очистите кэш и обновите приложение.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>The app is running slowly.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Clear the cache and update the app.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>应用运行缓慢。</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>请清除缓存并更新应用。</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2788,8 +6236,48 @@
           <t>Bizga murojaat qilganingizdan xursandmiz!</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Рахмат, ёрдамингиз учун!</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Бизга мурожаат қилганингиздан хурсандмиз!</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за вашу помощь!</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Мы рады, что вы обратились к нам!</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Thank you for your help!</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>We are glad that you contacted us!</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>感谢您的帮助！</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>我们很高兴您联系我们！</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2815,8 +6303,48 @@
           <t>Ilovada batafsil ko'rsatilgan.</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма нечта товардан иборатлигини кўриш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Иловада батафсил кўрсатилган.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли увидеть, из скольких товаров состоит заказ?</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Подробная информация отображается в приложении.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Can I see how many items are in the order?</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Detailed information is shown in the app.</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>可以查看订单包含多少商品吗？</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>应用中会详细显示。</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2842,8 +6370,48 @@
           <t>Xitoycha stiker orqali.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулотнинг асл нусхалигини қандай текшираман?</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Хитойча стикер орқали.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Как проверить оригинальность товара?</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Через китайский стикер.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>How can I check the authenticity of the product?</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Through the Chinese sticker.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>如何验证产品真伪？</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>通过中国贴纸检查。</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2869,8 +6437,48 @@
           <t>Manzilni yuboring, aniqlashtiramiz.</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Пунктга ўзим бориб оламан.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Манзилни юборинг, аниқлаштирамиз.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Я сам заберу из пункта.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте адрес, мы уточним.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>I will pick it up from the point myself.</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Send the address, we will clarify.</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>我想自己去自提点取货。</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>请发送地址，我们会帮您确认。</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2896,8 +6504,48 @@
           <t>Qolganini boshqa kartadan to'lang.</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Балансдаги пул етарли эмас.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Қолганини бошқа картадан тўланг.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Денег на балансе недостаточно.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Оплатите остаток с другой карты.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>There is not enough money in the balance.</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Pay the remaining amount from another card.</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>余额不足。</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>剩余金额请用其他银行卡支付。</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2923,8 +6571,48 @@
           <t>Mutaxassis bilan tekshiramiz.</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани қайта фаоллаштириш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Мутахассис билан текширамиз.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли повторно активировать заказ?</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Проверим с специалистом.</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Can the order be reactivated?</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>We will check with a specialist.</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>可以重新激活订单吗？</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>我们会与专家一起检查。</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2950,8 +6638,48 @@
           <t>Muammoni batafsil yozing.</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Хизмат сифатидан норозиман.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Муаммони батафсил ёзинг.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Я недоволен качеством обслуживания.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Опишите проблему подробно.</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>I am dissatisfied with the service quality.</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Please describe the problem in detail.</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>我对服务质量不满意。</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>请详细描述问题。</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2977,8 +6705,48 @@
           <t>Raqam yuboring.</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма чет элда қолиб кетган.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Рақамни юборинг.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Заказ застрял за границей.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>The order is stuck abroad.</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Send the order number.</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>订单滞留在国外。</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3004,8 +6772,48 @@
           <t>Odatda 15-25% gacha.</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>B2B да чегирма қанча?</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Одатда 15-25% гача.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Какая скидка в B2B?</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Обычно до 15-25%.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>How much discount is there in B2B?</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Usually up to 15-25%.</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>B2B的折扣是多少？</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>通常15-25%折扣。</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3031,8 +6839,48 @@
           <t>Ilovada "Parolni tiklash" funksiyasidan foydalaning.</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Паролни унутдим.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Иловада "Паролни тиклаш" функциясидан фойдаланинг.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Я забыл пароль.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Воспользуйтесь функцией «Восстановить пароль» в приложении.</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>I forgot my password.</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Use the "Reset Password" function in the app.</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>我忘记密码了。</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>请使用应用中的“重置密码”功能。</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3058,8 +6906,48 @@
           <t>Har doim yordam berishga tayyormiz.</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Саволларим учун рахмат!</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Ҳар доим ёрдам беришга тайёрмиз.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за вопросы!</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Мы всегда готовы помочь!</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Thank you for my questions!</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>We are always ready to help!</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>感谢我的提问！</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>我们随时准备提供帮助！</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3085,8 +6973,48 @@
           <t>Tez orada yetib keladi.</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма ҳолати "Жўнатилган".</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Тез орада етиб келади.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Статус заказа "Отправлен".</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>В ближайшее время прибудет.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Order status "Shipped".</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>It will arrive soon.</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>订单状态“已发货”。</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>很快就会到达。</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3112,8 +7040,48 @@
           <t>Rasmlar bilan murojaat qiling.</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Товар кутилганидан фарқли.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Расмлар билан мурожаат қилинг.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Товар отличается от ожидаемого.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Обратитесь с фотографиями.</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>The item is different from expected.</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Contact us with photos.</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>商品与预期不符。</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>请带照片联系我们。</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3139,8 +7107,48 @@
           <t>Toshkent uchun kuryer xizmati.</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Энг тез етказиб бериш усули қайси?</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Тошкент учун курьер хизмати.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Какой самый быстрый способ доставки?</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Для Ташкента — курьерская служба.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>What is the fastest delivery method?</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Courier service for Tashkent.</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>最快的配送方式是什么？</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>塔什干使用快递服务。</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3166,8 +7174,48 @@
           <t>Ushbu chat orqali bemalol yozavering. Mutaxassislarimiz har doim yordam berishga tayyor!</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Яна бирор саволим бўлса қаерга ёзаман?</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Ушбу чат орқали бемалол ёзаверинг. Мутахассисларимиз ҳар доим ёрдам беришга тайёр!</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Если у меня возникнут ещё вопросы, куда писать?</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Пишите спокойно в этот чат. Наши специалисты всегда готовы помочь!</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>If I have any more questions, where should I write?</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Feel free to write in this chat. Our specialists are always ready to help!</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>如果我还有其他问题，应该写在哪里？</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>请随时在此聊天中留言。我们的专家随时准备帮助您！</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3193,8 +7241,48 @@
           <t>To'lov tasdiqlangandan keyin odatda 15-25 kun ichida yetib keladi. Aniqlik uchun buyurtma raqamini yuboring.</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма қанча вақтда келади деб ўйлайсиз?</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов тасдиқлангандан кейин одатда 15-25 кун ичида етиб келади. Аниқлик учун буюртма рақамини юборинг.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Как вы думаете, за сколько времени придёт заказ?</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>После подтверждения оплаты обычно товар прибывает в течение 15-25 дней. Для точности отправьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>How long do you think the order will take to arrive?</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>After payment confirmation, it usually arrives within 15-25 days. For accuracy, send the order number.</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>您觉得订单需要多长时间到达？</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>付款确认后通常15-25天内到达。如需准确信息，请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3220,8 +7308,48 @@
           <t>Sotuvchidan omborga yetkazish 3-7 kun davom etadi. Keyin Xitoydan kelishi 12-20 kun.</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Заказим ҳали йўлга чиқмади, неччи кунда чиқади?</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Сотувчидан омборга етказиш 3-7 кун давом этади. Кейин Хитойдан келиши 12-20 кун.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Мой заказ ещё не отправлен, через сколько дней отправят?</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Доставка от продавца на склад занимает 3-7 дней. Затем доставка из Китая — 12-20 дней.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>My order hasn't been shipped yet, when will it be shipped?</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Delivery from seller to warehouse takes 3-7 days. Then from China it takes 12-20 days.</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>我的订单还没发货，几天后能发货？</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>从卖家到仓库需要3-7天，然后从中国发货需要12-20天。</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3247,8 +7375,48 @@
           <t>Xitoydan jo'natilgandan keyin odatda 12-18 kun ichida Toshkentga yetib keladi.</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмам қачон Тошкентга етиб келади?</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Хитойдан жўнатилгандан кейин одатда 12-18 кун ичида Тошкентга етиб келади.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Когда мой заказ прибудет в Ташкент?</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>После отправки из Китая обычно прибывает в Ташкент в течение 12-18 дней.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>When will my order arrive in Tashkent?</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>After being shipped from China, it usually arrives in Tashkent within 12-18 days.</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>我的订单什么时候到塔什干？</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>从中国发货后通常12-18天内到达塔什干。</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3274,8 +7442,48 @@
           <t>Toshkentga kelgandan keyin pochta orqali 3-7 ish kuni ichida yetkaziladi.</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Вилоятга буюртма қанча вақтда боради?</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Тошкентга келгандан кейин почта орқали 3-7 иш куни ичида етказилади.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>За сколько времени заказ дойдёт до региона?</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>После прибытия в Ташкент — 3-7 рабочих дней через почту.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>How long will the order take to reach the region?</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>After arriving in Tashkent, it will be delivered via post within 3-7 business days.</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>订单需要多长时间到达地区？</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>到达塔什干后，通过邮政3-7个工作日内送达。</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3301,8 +7509,48 @@
           <t>Ko'pincha Xitoy bayramlari, chegara yuklamasi yoki sotuvchi kechikishi sabab bo'ladi. Raqamni yuboring.</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма кечикиб кетяпти, сабаби нима бўлиши мумкин?</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Кўпинча Хитой байрамлари, чегара юкламаси ёки сотувчи кечикиши сабаб бўлади. Рақамни юборинг.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Заказ задерживается, какая может быть причина?</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Чаще всего причина — китайские праздники, загруженность границы или задержка продавца. Отправьте номер.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>The order is delayed, what could be the reason?</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Most often due to Chinese holidays, border congestion or seller delay. Send the number.</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>订单延误了，可能是什么原因？</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>最常见的原因是中国节假日、边境繁忙或卖家延误。请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3328,8 +7576,48 @@
           <t>Buyurtma DG yoki tracking raqamini yuboring, darhol tekshirib holatini aytaman.</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Менинг буюртмам қаерда ҳозир?</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма DG ёки tracking рақамини юборинг, дарҳол текшириб ҳолатини айтаман.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Где сейчас мой заказ?</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте DG или трекинг-номер заказа, я сразу проверю и скажу статус.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Where is my order now?</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Send the DG or tracking number of the order, I will check and tell the status immediately.</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>我的订单现在在哪里？</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单DG号或跟踪号，我会立即检查并告知状态。</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3355,8 +7643,48 @@
           <t>Bu vaqtinchalik holat bo'lishi mumkin. Raqamni yozing, tekshirib beramiz.</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Заказим статуси ўзгармаяпти, нима қилай?</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Бу вақтинчалик ҳолат бўлиши мумкин. Рақамни ёзинг, текшириб берамиз.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Статус заказа не меняется, что делать?</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Это может быть временная ситуация. Напишите номер, мы проверим.</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>My order status is not changing, what should I do?</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>This may be a temporary situation. Write the number, we will check.</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>订单状态没有变化，怎么办？</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>这可能是暂时情况。请写下订单号，我们会帮您检查。</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3382,8 +7710,48 @@
           <t>Ba'zida texnik sabablarga ko'ra shunday bo'ladi. DG raqamini bersangiz aniqlashtiramiz.</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма "Номаълум ҳолат" чиқяпти, бу нормалми?</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Баъзида техник сабабларга кўра шундай бўлади. DG рақамини берсангиз аниқлаштирамиз.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Заказ показывает "Неизвестный статус", это нормально?</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Иногда это бывает по техническим причинам. Отправьте DG номер, мы уточним.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>The order shows "Unknown status", is this normal?</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Sometimes this happens for technical reasons. Send the DG number and we will clarify.</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>订单显示“未知状态”，这正常吗？</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>有时由于技术原因会出现这种情况。请发送DG号，我们会帮您确认。</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3409,8 +7777,48 @@
           <t>Uzr so'raymiz. Buyurtma raqamlarini yuboring, holatni tekshirib yechim topamiz.</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Бир ой олдин заказ қилганман, ҳали келмади</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Узр сўраймиз. Буюртма рақамларини юборинг, ҳолатни текшириб ечим топамиз.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Я сделал заказ месяц назад, он ещё не пришёл</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Приносим извинения. Отправьте номера заказов, мы проверим статус и найдём решение.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>I placed an order a month ago, it still hasn't arrived</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>We apologize. Send the order numbers, we will check the status and find a solution.</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>我一个月前下的订单，还没收到</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>我们深表歉意。请发送订单号，我们会检查状态并提供解决方案。</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3436,8 +7844,48 @@
           <t>DG raqamini yuboring, mutaxassislarimiz izlab topishga harakat qiladi.</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Заказим йўқолган шекилли, қандай топиш мумкин?</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>DG рақамини юборинг, мутахассисларимиз излаб топишга ҳаракат қилади.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Похоже, мой заказ потерялся, как можно найти?</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте DG номер, наши специалисты постараются его найти.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>It seems my order is lost, how can I find it?</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Send the DG number, our specialists will try to find it.</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>我的订单好像丢失了，怎么找？</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>请发送DG号，我们的专家会努力查找。</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3463,8 +7911,48 @@
           <t>Pul balansingizga tushgan bo'lishi mumkin. Balansni tekshiring.</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Пул ечилди лекин буюртма яратилмади</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Пул балансингизга тушган бўлиши мумкин. Балансни текширинг.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Деньги списались, но заказ не создался</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Деньги могли поступить на ваш баланс. Проверьте баланс.</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Money was debited but the order was not created</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>The money may have been credited to your balance. Check your balance.</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>钱扣了但订单没创建</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>款项可能已进入您的余额。请检查余额。</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3490,8 +7978,48 @@
           <t>Ortiqcha summasini balansga qaytaramiz. Buyurtma raqamini yuboring.</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Икки марта пул ечилди, нима қиламан?</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Ортиқча суммасини балансга қайтарамиз. Буюртма рақамини юборинг.</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Деньги списались дважды, что делать?</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Излишек вернём на баланс. Отправьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Money was debited twice, what should I do?</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>We will refund the excess to the balance. Send the order number.</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>钱被扣了两次，怎么办？</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>多扣的金额会退回到余额。请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3517,8 +8045,48 @@
           <t>Ba'zida 1-2 soat vaqt oladi. Balansni yangilab ko'ring.</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов қилдим, лекин ҳали тасдиқланмади</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Баъзида 1-2 соат вақт олади. Балансни янглаб кўринг.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Я оплатил, но заказ ещё не подтверждён</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Иногда это занимает 1-2 часа. Обновите баланс.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>I paid, but the order is not confirmed yet</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Sometimes it takes 1-2 hours. Refresh your balance.</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>我已付款，但订单还未确认</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>有时需要1-2小时。请刷新余额查看。</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3544,8 +8112,48 @@
           <t>Boshqa karta sinab ko'ring yoki balansdan foydalaning.</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Карта орқали тўлов ўтмаяпти</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Бошқа карта синаб кўринг ёки балансдан фойдаланинг.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Оплата картой не проходит</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Попробуйте другую карту или оплатите с баланса.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Payment via card is not going through</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Try another card or pay from your balance.</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>银行卡支付失败</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>请尝试其他银行卡或使用余额支付。</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3571,8 +8179,48 @@
           <t>Balansdagi pulni yangi buyurtma berganingizda avtomatik ishlatiladi.</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Балансга пул қайтди, энди нима қиламан?</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Балансдаги пулни янги буюртма берганингизда автоматик ишлатилади.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Деньги вернулись на баланс, что теперь делать?</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Деньги с баланса автоматически используются при оформлении нового заказа.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Money has been returned to my balance, what should I do now?</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>The balance money will be automatically used when you place a new order.</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>钱已退回到余额，现在怎么办？</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>余额中的钱会在您下新订单时自动使用。</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3598,8 +8246,48 @@
           <t>Uzr so'raymiz. DG raqami, xitoycha stiker va foto yuboring.</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Келтирилган маҳсулот менинг заказимга мос эмас</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Узр сўраймиз. DG рақами, хитойча стикер ва фото юборинг.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Полученный товар не соответствует моему заказу</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Приносим извинения. Отправьте DG номер, китайский стикер и фото.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>The received product does not match my order</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>We apologize. Send the DG number, Chinese sticker and photo.</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>收到的商品与我的订单不符</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>我们深表歉意。请发送DG号、中国贴纸和照片。</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3625,8 +8313,48 @@
           <t>Ha, foto va video bilan DG raqamini yuboring, tezda hal qilamiz.</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Товар брак чиқди, алмаштириш мумкинми?</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, фото ва видео билан DG рақамини юборинг, тезда ҳал қиламиз.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Товар оказался бракованным, можно ли заменить?</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Да, отправьте фото и видео вместе с DG номером, мы быстро решим вопрос.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>The item turned out to be defective, can it be replaced?</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Yes, send photos and video along with the DG number, we will resolve it quickly.</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>商品是残次品，可以更换吗？</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>可以，请发送照片和视频以及DG号，我们会尽快处理。</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3652,8 +8380,48 @@
           <t>Rasmlar bilan murojaat qiling, almashtirish yoki qaytarishni ko'rib chiqamiz.</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Ранги бошқача келди, нима қилишим мумкин?</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Расмлар билан мурожаат қилинг, алмаштириш ёки қайтаришни кўриб чиқамиз.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Пришёл товар другого цвета, что я могу сделать?</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Обратитесь с фотографиями, мы рассмотрим замену или возврат.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>The item came in a different color, what can I do?</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Contact us with photos, we will consider replacement or return.</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>商品颜色不对，我该怎么办？</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>请带照片联系我们，我们会考虑更换或退货。</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3679,8 +8447,48 @@
           <t>Foto bilan DG raqamini yuboring, yechim topamiz.</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Ўлчами кичик келди</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Фото билан DG рақамини юборинг, ечим топамиз.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Размер оказался маленьким</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте фото и DG номер, мы найдём решение.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>The size came out small</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Send a photo with the DG number, we will find a solution.</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>尺寸偏小</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>请发送照片和DG号，我们会帮您解决。</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3706,8 +8514,48 @@
           <t>Muammoni batafsil yozing va rasmlarni ilova qiling.</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот сифати жуда паст</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Муаммони батафсил ёзинг ва расмларни илова қилинг.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Качество товара очень низкое</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Опишите проблему подробно и приложите фотографии.</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>The product quality is very low</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Describe the problem in detail and attach photos.</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>产品质量很差</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>请详细描述问题并附上照片。</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3733,8 +8581,48 @@
           <t>Brak yoki noto'g'ri tovar bo'lsa — ha. Rasmlar va DG raqam kerak.</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Товарни қайтариб, пулни қайтариб берсангиз бўладими?</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Брак ёки нотоғри товар бўлса — ҳа. Расмлар ва DG рақам керак.</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли вернуть товар и получить обратно деньги?</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Если товар бракованный или неправильный — да. Нужны фото и DG номер.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Can I return the item and get a refund?</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>If the item is defective or incorrect — yes. Photos and DG number are required.</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>可以退货并退款吗？</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>如果是残次品或错误商品——可以。需要照片和DG号。</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3760,8 +8648,48 @@
           <t>Odatda yetkazib berilgandan keyin 14 kun ichida murojaat qilish tavsiya etiladi.</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Қайтариш учун қанча вақт бор?</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Одатда етказиб берилгандан кейин 14 кун ичида мурожаат қилиш тавсия этилади.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени есть на возврат?</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Обычно рекомендуется обращаться в течение 14 дней после получения товара.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>How much time do I have for return?</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>It is recommended to apply within 14 days after delivery.</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>退货期限是多久？</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>通常建议在收到商品后14天内申请。</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3787,8 +8715,48 @@
           <t>Rasmlar tasdiqlangandan keyin odatda 48 soat ichida balansga tushadi.</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Пул қайтарилгунча қанча вақт кетади?</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Расмлар тасдиқлангандан кейин одатда 48 соат ичида балансга тушади.</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает возврат денег?</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>После подтверждения фото обычно деньги поступают на баланс в течение 48 часов.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>How long does it take for the refund to be processed?</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>After photos are approved, it usually credits to the balance within 48 hours.</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>退款需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>照片审核通过后，通常在48小时内退回到余额。</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3814,8 +8782,48 @@
           <t>Ha, B2B bo'limida narxlar odatda 20% gacha arzonroq.</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Улгуржи сотиб олсам нархи арзонроқ бўладими?</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, B2B бўлимида нархлар одатда 20% гача арзонроқ.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Будет ли цена дешевле при оптовой покупке?</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Да, в разделе B2B цены обычно на 20% дешевле.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Will the price be cheaper if I buy wholesale?</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Yes, in the B2B section prices are usually up to 20% cheaper.</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>批发购买会更便宜吗？</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>是的，B2B部分的价格通常便宜20%以内。</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3841,8 +8849,48 @@
           <t>Yo'q, pasport ma'lumotlari yetarli.</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>B2B да ҳужжат талаб қилинадими?</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Йўқ, паспорт маълумотлари етарли.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Требуются ли документы для B2B?</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Нет, достаточно паспортных данных.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Are documents required for B2B?</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>No, passport details are sufficient.</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>B2B需要提供文件吗？</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>不需要，只需护照信息。</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3868,8 +8916,48 @@
           <t>Yo'q, B2B da har kg uchun kargo to'lovi mavjud.</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>B2B да 7 кг гача бепул етказиб бериш борми?</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Йўқ, B2B да ҳар кг учун карго тўлови мавжуд.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Есть ли бесплатная доставка до 7 кг в B2B?</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Нет, в B2B за каждый кг взимается плата за карго.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Is there free delivery up to 7 kg in B2B?</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>No, in B2B there is a cargo fee for each kg.</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>B2B有7公斤内免费配送吗？</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>没有，B2B中每公斤都需要支付货物费用。</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3895,8 +8983,48 @@
           <t>Ilovani yangilang, cache ni tozalang. Muammo davom etsa skrinshot yuboring.</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Илова хато берса нима қилай?</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Иловани янгиланг, cache ни тозаланг. Муаммо давом этса скриншот юборинг.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Что делать, если приложение выдаёт ошибку?</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Обновите приложение, очистите кэш. Если проблема остаётся — отправьте скриншот.</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>What should I do if the app gives an error?</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Update the app and clear the cache. If the problem persists, send a screenshot.</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>应用报错怎么办？</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>请更新应用并清除缓存。如果问题持续，请发送截图。</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3922,8 +9050,48 @@
           <t>Bu chat orqali DG raqamini yuboring, biz tekshirib beramiz.</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>SMS келмаяпти, буюртма ҳолатини қандай биламан?</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Бу чат орқали DG рақамини юборинг, биз текшириб берамиз.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>SMS не приходит, как узнать статус заказа?</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте DG номер в этот чат, мы проверим.</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>SMS is not coming, how can I know the order status?</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Send the DG number through this chat, we will check it for you.</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>收不到短信，如何查询订单状态？</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>请在此聊天发送DG号，我们会帮您查询。</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3949,8 +9117,48 @@
           <t>Ilovani qayta ishga tushiring yoki yangilang.</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Балансдаги пул кўринмаяпти</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Иловани қайта ишга туширинг ёки янгиланг.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Деньги на балансе не отображаются</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Перезапустите приложение или обновите его.</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>The money in the balance is not visible</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Restart or update the app.</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>余额金额不显示</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>请重新启动或更新应用。</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3976,8 +9184,48 @@
           <t>Bu yerda yozing, men yordam beraman yoki mutaxassisni chaqiraman.</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Оператор жавоб бермаяпти, ёрдам берсангиз?</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Бу ерда ёзинг, мен ёрдам бераман ёки мутахассисни чақираман.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Оператор не отвечает, можете помочь?</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Напишите здесь, я помогу или вызову специалиста.</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>The operator is not responding, can you help?</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Write here, I will help or call a specialist.</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>客服没有回复，你能帮忙吗？</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>请在这里留言，我会帮助您或呼叫专家。</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4003,8 +9251,48 @@
           <t>Qaysi savolingiz bor? Batafsil yozing.</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Етказиб бериш ҳақида батафсил маълумот керак</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Қайси саволингиз бор? Батафсил ёзинг.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Нужна подробная информация о доставке</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Какой у вас вопрос? Напишите подробно.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>I need detailed information about delivery</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>What is your question? Write in detail.</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>需要详细的配送信息</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>您有什么问题？请详细说明。</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4030,8 +9318,48 @@
           <t>Qanday mahsulot haqida maslahat kerak? Rasm yuborsangiz yordam beraman.</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот ҳақида маслаҳат берсангиз бўладими?</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Қандай маҳсулот ҳақида маслаҳат керак? Расм юборсангиз ёрдам бераман.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Можете дать совет по товару?</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>По какому товару нужен совет? Если отправите фото, помогу.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Can you give advice about the product?</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>What product do you need advice on? If you send a photo, I can help.</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>可以给我产品建议吗？</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>您需要哪种产品的建议？如果发送照片，我可以帮忙。</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4057,8 +9385,48 @@
           <t>Ko'pincha yetkazib berish muddatlari va ba'zi tovarlarning sifati bo'yicha murojaatlar keladi.</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Саҳийда энг кўп муаммо қаерда бўлади?</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Кўпинча етказиб бериш муддатлари ва баъзи товарларнинг сифати бўйича мурожаатлар келади.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Где чаще всего возникают проблемы в Sahiy?</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Чаще всего обращения по срокам доставки и качеству некоторых товаров.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Where do most problems occur in Sahiy?</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Most often, requests come regarding delivery times and the quality of some products.</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy最常见的问题是什么？</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>最常见的是关于配送时间和部分产品质量的问题。</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4084,8 +9452,48 @@
           <t>Bu yerga yozing, rahbariyatga yetkazamiz.</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Таклифим бор, қаерга ёзаман?</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Бу ерга ёзинг, раҳбариятга етказамиз.</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>У меня есть предложение, куда написать?</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Напишите сюда, мы передадим руководству.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>I have a suggestion, where should I write?</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Write here, we will forward it to the management.</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>我有建议，应该写在哪里？</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>请写在这里，我们会转交给管理层。</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4111,8 +9519,48 @@
           <t>Punkt manzili va telefon raqamini yuboring, yordam beramiz.</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма пунктга келди, лекин мен ола олмаяпман</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Пункт манзили ва телефон рақамини юборинг, ёрдам берамиз.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Заказ прибыл в пункт, но я не могу его забрать</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте адрес пункта и номер телефона, мы поможем.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>The order has arrived at the point, but I can't pick it up</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Send the pickup point address and phone number, we will help.</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>订单已到自提点，但我无法取货</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>请发送自提点地址和电话号码，我们会帮忙。</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4138,8 +9586,48 @@
           <t>Hali jo'natilmagan bo'lsa o'zgartirish mumkin, raqamni yuboring.</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Заказимни бошқа манзилга ўзгартирса бўладими?</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Ҳали жўнатилмаган бўлса ўзгартириш мумкин, рақамни юборинг.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли изменить адрес заказа?</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Если заказ ещё не отправлен, его можно изменить. Отправьте номер.</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Can I change my order to another address?</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>If the order has not been shipped yet, it can be changed. Send the number.</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>可以更改订单地址吗？</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>如果订单尚未发货，可以更改。请发送订单号。</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4165,8 +9653,48 @@
           <t>Kelmay qolgan zakaz raqamini yozing.</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>2 та бир хил заказ қилганман, бири келди бири йўқ</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Келмай қолган заказ рақамини ёзинг.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Я сделал 2 одинаковых заказа, один пришёл, другого нет</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Напишите номер заказа, который не пришёл.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>I placed 2 identical orders, one arrived, the other didn't</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Write the number of the order that didn't arrive.</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>我下了2个相同的订单，一个到了，另一个没到</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>请写下未到达订单的编号。</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4192,8 +9720,48 @@
           <t>Ilovadagi buyurtma ichida yoki to'lov tarixida saqlanadi.</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Тўлов чекини қаердан топаман?</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Иловадаги буюртма ичида ёки тўлов тарихида сақланади.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Где найти чек оплаты?</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Чек сохраняется внутри заказа в приложении или в истории платежей.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Where can I find the payment receipt?</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>It is saved inside the order in the app or in the payment history.</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>在哪里找到支付凭证？</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>在应用订单详情或支付记录中可以找到。</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4219,8 +9787,48 @@
           <t>Yangi tovar tanlab, eski DG raqamini yozib yuboring.</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Товарни алмаштириш учун нима қилиш керак?</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Янги товар танлаб, эски DG рақамини ёзиб юборинг.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Что нужно сделать для замены товара?</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Выберите новый товар и напишите старый DG номер.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>What do I need to do to exchange the item?</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Choose a new item and write the old DG number.</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>换货需要做什么？</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>请选择新商品并写下旧的DG号。</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4246,8 +9854,48 @@
           <t>Buyurtma DG raqamini yuboring, mutaxassislarimiz sotuvchi bilan bog'lanib tekshiradi.</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмам неччи кундан бери йўлда, лекин ҳолати ўзгармаяпти?</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма DG рақамини юборинг, мутахассисларимиз сотувчи билан боғланиб текширади.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Заказ уже много дней в пути, но статус не меняется?</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Отправьте DG номер заказа, наши специалисты свяжутся с продавцом и проверят.</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>My order has been on the way for many days, but the status is not changing?</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Send the DG number of the order, our specialists will contact the seller and check.</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>订单已经在路上很多天了，但状态没有变化？</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>请发送订单DG号，我们的专家会联系卖家进行检查。</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4273,8 +9921,48 @@
           <t>Sahiy — Xitoydan millionlab turdagi tovarlarni onlayn buyurtma qiladigan platforma. Buyurtma berganingizdan keyin odatda 12–15 kun ichida yetib keladi; viloyatlarda 20 kungacha cho'zilishi mumkin.</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий қандай компания?</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий — Хитойдан миллионлаб турдаги товарларни онлайн буюртма қиладиган платформа. Буюртма берганингиздан кейин одатда 12–15 кун ичида етиб келади; вилоятларда 20 кунгача чўзилиши мумкин.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Что за компания Sahiy?</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy — это платформа для онлайн-заказа миллионов видов товаров из Китая. Обычно после оформления заказа доставка занимает 12–15 дней, в регионах может занять до 20 дней.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>What kind of company is Sahiy?</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy is a platform for ordering millions of different products from China online. After placing an order, it usually arrives within 12–15 days; in regions, it may take up to 20 days.</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy是什么公司？</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy是从中国在线订购数百万种商品的平台。下单后通常12-15天内到达；地区可能需要最多20天。</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4300,8 +9988,48 @@
           <t>Sahiy — Xitoydan millionlab turdagi tovarlarni onlayn buyurtma qiladigan platforma. Buyurtma berganingizdan keyin odatda 12–15 kun ichida yetib keladi; viloyatlarda 20 kungacha cho'zilishi mumkin.</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий нима?</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий — Хитойдан миллионлаб турдаги товарларни онлайн буюртма қиладиган платформа. Буюртма берганингиздан кейин одатда 12–15 кун ичида етиб келади; вилоятларда 20 кунгача чўзилиши мумкин.</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Что такое Sahiy?</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy — это платформа для онлайн-заказа миллионов видов товаров из Китая. Обычно после оформления заказа доставка занимает 12–15 дней, в регионах может занять до 20 дней.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>What is Sahiy?</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy is a platform for ordering millions of different products from China online. After placing an order, it usually arrives within 12–15 days; in regions, it may take up to 20 days.</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy是什么？</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy是从中国在线订购数百万种商品的平台。下单后通常12-15天内到达；地区可能需要最多20天。</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4327,8 +10055,48 @@
           <t>Ha. Tovar singan yoki nuqsonli kelsa, foto yuboring — almashtiramiz yoki pulni qaytaramiz. 14 kun ichida ham original holatda qaytarish mumkin.</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма синган келса қайтариб оласизларми?</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа. Товар синган ёки нуқсонли келса, фото юборинг — алмаштирамиз ёки пулни қайтарамиз. 14 кун ичида ҳам оригинал ҳолатда қайтариш мумкин.</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Если заказ пришёл разбитым, вы заберёте обратно?</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Да. Если товар пришёл разбитым или с дефектом, отправьте фото — мы заменим или вернём деньги. Также возможен возврат в оригинальном состоянии в течение 14 дней.</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>If the order arrives broken, will you take it back?</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Yes. If the item arrives broken or defective, send a photo — we will replace or refund. Return in original condition is also possible within 14 days.</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>如果订单损坏送达，你们会回收吗？</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>是的。如果商品损坏或有缺陷，请发送照片——我们会更换或退款。14天内也可以原状退货。</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4346,18 +10114,58 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
+          <t>Assalomu alaykum!</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum!</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
           <t>Ассалому алайкум!</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>Ассалому алайкум!</t>
         </is>
       </c>
-      <c r="F145" t="n">
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум!</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум!</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum!</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum!</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>你好！</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>你好！</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
         <v>1</v>
       </c>
-      <c r="G145" t="n">
+      <c r="O145" t="n">
         <v>58</v>
       </c>
     </row>
@@ -4382,13 +10190,53 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
+          <t>Xitoy mutaxassislariga yozdik tez orada ijobiy hal qilib berishadi, 2 kun oralig'ida yuborishadi.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Хитой сотувчи</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
           <t>Хитой мутахассисларига ёздик тез орада ижобий ҳал қилиб беришади, 2 кун оралиғида юборишади.</t>
         </is>
       </c>
-      <c r="F146" t="n">
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Китайский продавец</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Мы написали китайским специалистам, в ближайшее время они решат вопрос положительно и отправят в течение 2 дней.</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Chinese seller</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>We have written to the Chinese specialists, they will resolve the issue positively soon and send it within 2 days.</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>中国卖家</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>我们已联系中国专家，他们会尽快积极解决，并在2天内发货。</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
         <v>1</v>
       </c>
-      <c r="G146" t="n">
+      <c r="O146" t="n">
         <v>98</v>
       </c>
     </row>
@@ -4408,18 +10256,58 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
+          <t>Buyurtma olib ketilgan!</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Buyurtma kurer orqali etkazib berish uchun olib ketilgan!</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>Буюртма олиб кетилган!</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Буюртма курер орқали етказиб бериш учун олиб кетилган!</t>
         </is>
       </c>
-      <c r="F147" t="n">
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Заказ забрали!</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Заказ забрали для доставки через курьера!</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Order has been picked up!</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>The order has been picked up for courier delivery!</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>订单已被取走！</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>订单已被取走，用于快递配送！</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
         <v>1</v>
       </c>
-      <c r="G147" t="n">
+      <c r="O147" t="n">
         <v>88</v>
       </c>
     </row>
@@ -4447,10 +10335,50 @@
           <t>Hurmatli mijoz sizga qanday yordam bera olaman menga batafsil malumot yozing iloji bo`lsa buyurtma raqamini yozing</t>
         </is>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>ёрдам</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Ҳурматли мижоз сизга қандай ёрдам бера оламан менга батафсил маълумот ёзинг иложи бўлса буюртма рақамини ёзинг</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>помощь</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Уважаемый клиент, чем я могу вам помочь? Напишите подробную информацию, по возможности укажите номер заказа.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Dear customer, how can I help you? Please write detailed information, if possible, indicate the order number.</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>帮助</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的客户，我能为您提供什么帮助？请详细描述信息，如果可能，请写下订单号。</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
         <v>1</v>
       </c>
-      <c r="G148" t="n">
+      <c r="O148" t="n">
         <v>87</v>
       </c>
     </row>
@@ -4478,10 +10406,50 @@
           <t>Yaxshi, tekshirib ko'ramiz. Buyurtma raqamingizni yozing.</t>
         </is>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Текширамиз</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Яхши, текшириб кўрамиз. Буюртма рақамингизни ёзинг.</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Проверим</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Хорошо, проверим. Напишите номер вашего заказа.</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>We'll check</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Okay, we'll check. Please write your order number.</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>我们会检查</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>好的，我们会检查。请写下您的订单号。</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
         <v>1</v>
       </c>
-      <c r="G149" t="n">
+      <c r="O149" t="n">
         <v>46</v>
       </c>
     </row>
@@ -4509,10 +10477,50 @@
           <t>Sizga qanday yordam kerak? Muammoni batafsil yozing.</t>
         </is>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Ёрдам керакми?</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Сизга қандай ёрдам керак? Муаммони батафсил ёзинг.</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Нужна помощь?</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Какая помощь вам нужна? Опишите проблему подробно.</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Need help?</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>What help do you need? Describe the problem in detail.</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>需要帮助吗？</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>您需要什么帮助？请详细描述问题。</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
         <v>1</v>
       </c>
-      <c r="G150" t="n">
+      <c r="O150" t="n">
         <v>53</v>
       </c>
     </row>
@@ -4540,10 +10548,50 @@
           <t>Buyurtmangiz sotuvchida mahsulot qolmagani sababli bekor qilindi. Pul 48 soat ichida qaytariladi.</t>
         </is>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма бекор қилинди</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмангиз сотувчида маҳсулот қолмагани сабабли бекор қилинди. Пул 48 соат ичида қайтарилади.</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Заказ отменён</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Ваш заказ отменён, потому что у продавца не осталось товара. Деньги будут возвращены в течение 48 часов.</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Order cancelled</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Your order was cancelled because the product is out of stock at the seller. Money will be refunded within 48 hours.</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>订单已取消</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>您的订单因卖家缺货而取消。款项将在48小时内退还。</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
         <v>1</v>
       </c>
-      <c r="G151" t="n">
+      <c r="O151" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4571,10 +10619,50 @@
           <t>Ha, biz rasmiy saytmiz va butun O'zbekistonda filiallarimiz bor.</t>
         </is>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Расмий сайт</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, биз расмий сайтмиз ва бутун Ўзбекистонда филиалларимиз бор.</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Официальный сайт</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Да, мы официальный сайт и у нас есть филиалы по всему Узбекистану.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Official website</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Yes, we are the official website and we have branches throughout Uzbekistan.</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>官方网站</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>是的，我们是官方网站，在乌兹别克斯坦全国都有分公司。</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
         <v>1</v>
       </c>
-      <c r="G152" t="n">
+      <c r="O152" t="n">
         <v>44</v>
       </c>
     </row>
@@ -4602,10 +10690,50 @@
           <t>Sahiy dasturi → Profil → "Ulgurji xaridor bo'l" sahifasidan ro'yxatdan o'ting.</t>
         </is>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Улгуржи харидор</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий дастури → Профил → "Улгуржи харидор бўл" саҳифасидан рўйхатдан ўтинг.</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Оптовый покупатель</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Приложение Sahiy → Профиль → Страница "Стать оптовым покупателем".</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Wholesale buyer</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy app → Profile → Register from the "Become a wholesale buyer" page.</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>批发买家</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy应用 → 个人资料 → 从“成为批发买家”页面注册。</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
         <v>1</v>
       </c>
-      <c r="G153" t="n">
+      <c r="O153" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4633,10 +10761,50 @@
           <t>Sahiy dasturiga kiring → Profil → Til/Valyuta bo'limidan tilni o'zgartiring.</t>
         </is>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Тилни ўзгартириш</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий дастурига киринг → Профил → Тил/Валюта бўлимидан тилни ўзгартиринг.</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Сменить язык</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Зайдите в приложение Sahiy → Профиль → Раздел Язык/Валюта.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Change language</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Go to Sahiy app → Profile → Change language in the Language/Currency section.</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>更改语言</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>进入Sahiy应用 → 个人资料 → 在语言/货币部分更改语言。</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
         <v>1</v>
       </c>
-      <c r="G154" t="n">
+      <c r="O154" t="n">
         <v>47</v>
       </c>
     </row>
@@ -4664,10 +10832,50 @@
           <t>Mahsulot yo'lga chiqqandan keyin 12-15 kun ichida yetib keladi.</t>
         </is>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Етказиш муддати</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот йўлга чиққандан кейин 12-15 кун ичида етиб келади.</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Срок доставки</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>После отправки товара он обычно прибывает в течение 12-15 дней.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Delivery time</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>After the product is shipped, it usually arrives within 12-15 days.</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>配送时间</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>产品发货后通常12-15天内到达。</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
         <v>1</v>
       </c>
-      <c r="G155" t="n">
+      <c r="O155" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4695,10 +10903,50 @@
           <t>Yangilangan Sahiy ilovasidan buyurtma qilsangiz, yetkazish bepul.</t>
         </is>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Бепул етказиш</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Янгиланган Саҳий иловасидан буюртма қилсангиз, етказиш бепул.</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатная доставка</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Если оформить заказ через обновлённое приложение Sahiy, доставка бесплатная.</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Free delivery</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>If you order through the updated Sahiy app, delivery is free.</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>免费配送</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>通过更新后的Sahiy应用下单，配送免费。</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
         <v>1</v>
       </c>
-      <c r="G156" t="n">
+      <c r="O156" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4726,10 +10974,50 @@
           <t>Ma'lumot yig'ishimiz bilan sizga javob yozamiz. Buyurtma raqamini qoldiring.</t>
         </is>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Маълумот йиғамиз</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Маълумот йиғишимиз билан сизга жавоб ёзамиз. Буюртма рақамини қолдиринг.</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Собираем информацию</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Как только соберём информацию, напишем вам ответ. Оставьте номер заказа.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>We are collecting information</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Once we collect the information, we will write you a response. Please leave your order number.</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>我们正在收集信息</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>收集完信息后我们会回复您。请留下订单号。</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
         <v>1</v>
       </c>
-      <c r="G157" t="n">
+      <c r="O157" t="n">
         <v>50</v>
       </c>
     </row>
@@ -4757,10 +11045,50 @@
           <t>Mahsulot bizning manzilga yetib keldi. O'zingiz olib ketishingiz yoki yetkazib berishni buyurtma qilishingiz mumkin.</t>
         </is>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот етиб келди</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот бизнинг манзилга етиб келди. Ўзингиз олиб кетишингиз ёки етказиб беришни буюртма қилишингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Товар прибыл</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Товар прибыл на наш адрес. Вы можете забрать сами или заказать доставку.</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>The product has arrived</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>The product has arrived at our address. You can pick it up yourself or order delivery.</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>产品已到达</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>产品已到达我们的地址。您可以自提或下单配送。</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
         <v>1</v>
       </c>
-      <c r="G158" t="n">
+      <c r="O158" t="n">
         <v>51</v>
       </c>
     </row>
@@ -4788,10 +11116,50 @@
           <t>Operatorlarimiz tez orada siz bilan bog'lanadi.</t>
         </is>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Операторлар боғланади</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Операторларимиз тез орада сиз билан боғланади.</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Операторы свяжутся</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Наши операторы свяжутся с вами в ближайшее время.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Operators will contact you</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Our operators will contact you shortly.</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>客服将联系您</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>我们的客服很快会与您联系。</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
         <v>1</v>
       </c>
-      <c r="G159" t="n">
+      <c r="O159" t="n">
         <v>52</v>
       </c>
     </row>
@@ -4819,10 +11187,50 @@
           <t>To'langan pul 48 soat ichida hisobingizga qaytariladi.</t>
         </is>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Пул қайтарилади</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Тўланган пул 48 соат ичида ҳисобингизга қайтарилади.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Деньги вернут</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Оплаченные деньги будут возвращены на ваш счёт в течение 48 часов.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Money will be refunded</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>The paid money will be refunded to your account within 48 hours.</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>款项将退还</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>支付的款项将在48小时内退还到您的账户。</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
         <v>1</v>
       </c>
-      <c r="G160" t="n">
+      <c r="O160" t="n">
         <v>54</v>
       </c>
     </row>
@@ -4850,10 +11258,50 @@
           <t>Afsuski, hozircha to'lovsiz xarid qilish imkoni yo'q.</t>
         </is>
       </c>
-      <c r="F161" t="n">
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Тўловсиз харид йўқ</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Афсуски, ҳозирча тўловсиз харид қилиш имкони йўқ.</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Покупка без оплаты невозможна</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>К сожалению, в настоящее время покупка без оплаты невозможна.</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>No purchase without payment</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>Unfortunately, purchase without payment is not possible at the moment.</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>无法无付款购买</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>抱歉，目前无法无付款购买。</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
         <v>1</v>
       </c>
-      <c r="G161" t="n">
+      <c r="O161" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4881,10 +11329,50 @@
           <t>Balansingizdagi mablag'dan boshqa buyurtmalarni to'lashingiz mumkin.</t>
         </is>
       </c>
-      <c r="F162" t="n">
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Балансдан тўлаш</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Балансингиздаги маблағдан бошқа буюртмаларни тўлашингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Оплата с баланса</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Вы можете оплачивать другие заказы средствами с вашего баланса.</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>Pay from balance</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>You can pay for other orders from the funds in your balance.</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>从余额支付</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>您可以使用余额支付其他订单。</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
         <v>1</v>
       </c>
-      <c r="G162" t="n">
+      <c r="O162" t="n">
         <v>56</v>
       </c>
     </row>
@@ -4909,18 +11397,53 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Assalomu aleykum mahsulotni sahiy seller ilovamizga joylash uchun ushbu ilovani play market hamda app storedan yuklab olishingiz yoki kompyuter variantimiz orqali seller sahiy uz deb qidiruv berish orqali undan ro'yxatdan o'tasiz 
-ro'yxatdan o'tish uchun siz telefon raqami hamda o'zingiz uchun qulay yodingizda qoladigan parol kiritasiz hamda ro'yxatdan o'tgach do'konlar bo'limi orqali do'kon yaratish tugmasini yuqoridan bosasiz 
-u joyda sizda do'koningi uchun nom kiritish hamda surat yuklash hamda ta'rif yani do'kon haqida (sifatli ,arzon,eng zo'ri,daxshat kabi hamda qo'pol ta'riflar kiritlmagan) ta'rif yozasiz pastki qismidan ruscha ta'rifniham berib o'tasiz 
-shundan so'ng do'kon uchun rasm qo'shish kerakligi so'raladi siz galereyadan yoki kamera yordamida do'koningiz uchun nomiga undagi mavjud mahsulotlarga xos bo'lgan rasmni yuklashingiz shart bo'ladi( do'kon suratida boshqa logotiplar , mos bo'lmagan suratlar, taqiqlangan turli xildagi suratlar,sifatsiz suratlar yuklash taqiqlanadi) 
-shundan so'ng sizdan do'kon manzilini belgilash so'raladi siz xaritalar orqali joyni belgilashingiz shart bo'ladi 
-va tasdiqlash orqali do'koningiz muvaffaqiyatli yaratiladi</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
+          <t>Assalomu aleykum mahsulotni sahiy seller ilovamizga joylash uchun ushbu ilovani play market hamda app storedan yuklab olishingiz yoki kompyuter variantimiz orqali seller sahiy uz deb qidiruv berish orqali undan ro'yxatdan o'tasiz ro'yxatdan o'tish uchun siz telefon raqami hamda o'zingiz uchun qulay yodingizda qoladigan parol kiritasiz hamda ro'yxatdan o'tgach do'konlar bo'limi orqali do'kon yaratish tugmasini yuqoridan bosasiz u joyda sizda do'koningi uchun nom kiritish hamda surat yuklash hamda ta'rif yani do'kon haqida (sifatli ,arzon,eng zo'ri,daxshat kabi hamda qo'pol ta'riflar kiritlmagan) ta'rif yozasiz pastki qismidan ruscha ta'rifniham berib o'tasiz shundan so'ng do'kon uchun rasm qo'shish kerakligi so'raladi siz galereyadan yoki kamera yordamida do'koningiz uchun nomiga undagi mavjud mahsulotlarga xos bo'lgan rasmni yuklashingiz shart bo'ladi( do'kon suratida boshqa logotiplar , mos bo'lmagan suratlar, taqiqlangan turli xildagi suratlar,sifatsiz suratlar yuklash taqiqlanadi) shundan so'ng sizdan do'kon manzilini belgilash so'raladi siz xaritalar orqali joyni belgilashingiz shart bo'ladi va tasdiqlash orqali do'koningiz muvaffaqiyatli yaratiladi</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот жойлаш</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Ассалому алейкум маҳсулотни саҳий seller иловамизга жойлаш учун ушбу иловани play market ҳамда app storedан юклаб олишингиз ёки компьютер вариантимиз орқали seller sahiy uz деб қидирув бериш орқали ундан рўйхатдан ўтасиз рўйхатдан ўтиш учун сиз телефон рақами ҳамда ўзингиз учун қулай ёдингизда қолдиган парол киритасиз ҳамда рўйхатдан ўтгач дўконлар бўлими орқали дўкон яратиш тугмасини юқоридан босасиз у жойда сизда дўконингиз учун ном киритиш ҳамда сурат юклаш ҳамда таъриф яъни дўкон ҳақида (сифатли, арзон, энг зўри, даҳшат каби ҳамда қўпол таърифлар киритилмаган) таъриф ёзасиз пастки қисмидан русча таърифни ҳам бериб ўтасиз шундан сўнг дўкон учун расм қўшиш кераклиги сўралади сиз галереядан ёки камера ёрдамида дўконингиз учун номига ундаги мавжуд маҳсулотларга хос бўлган расмни юклашингиз шарт бўлади (дўкон суратида бошқа логотиплар, мос бўлмаган суратлар, тақиқланган турли хилдаги суратлар, сифатсиз суратлар юклаш тақиқланади) шундан сўнг сиздан дўкон манзилини белгилаш сўралади сиз харита орқали жойни белгилашингиз шарт бўлади ва тасдиқлаш орқали дўконингиз муваффақиятли яратилади</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Размещение товара</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум. Для размещения товара в приложении Sahiy Seller вы можете скачать приложение из Play Market или App Store, либо через компьютерную версию, найдя seller sahiy uz и зарегистрироваться. Для регистрации введите номер телефона и удобный для вас пароль. После регистрации в разделе «Магазины» нажмите кнопку создания магазина сверху. Там введите название магазина, загрузите фото и напишите описание (качественный, недорогой, самый лучший и т.д., без грубых выражений). Также укажите русское описание. Затем загрузите фото магазина (запрещено загружать другие логотипы, неподходящие, запрещённые или некачественные изображения). После этого укажите адрес магазина на карте и подтвердите — магазин будет успешно создан.</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>Product Placement</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum. To place a product in our Sahiy Seller app, download the app from Play Market or App Store, or search for "seller sahiy uz" on the computer version and register. For registration, enter your phone number and a memorable password. After registration, go to the Stores section and click the Create Store button at the top. There, enter the store name, upload a photo, and write a description (quality, cheap, the best, etc., without rude words). Also provide a Russian description. Then upload a photo of the store (other logos, inappropriate, prohibited or low-quality images are not allowed). After that, mark the store address on the map and confirm — your store will be successfully created.</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>上架产品</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>您好，要在Sahiy Seller应用中上架产品，请从Play Market或App Store下载应用，或通过电脑版搜索seller sahiy uz进行注册。注册时输入手机号和易记密码。注册后在“商店”部分点击上方“创建商店”按钮。在那里输入商店名称、上传照片并写描述（优质、便宜、最好等，不含粗俗描述）。同时提供俄文描述。然后上传商店照片（禁止上传其他logo、不合适、违规或低质量图片）。之后在地图上标记商店地址并确认，您的商店即可成功创建。</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
         <v>1</v>
       </c>
-      <c r="G163" t="n">
+      <c r="O163" t="n">
         <v>59</v>
       </c>
     </row>
@@ -4948,10 +11471,50 @@
           <t>Buyurtmalaringizni Profil → Buyurtmalarim bo'limidan kuzating.</t>
         </is>
       </c>
-      <c r="F164" t="n">
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Буюртма ҳолати</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмаларингизни Профил → Буюртмаларим бўлимидан кузатинг.</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Статус заказа</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Отслеживайте свои заказы в разделе Профиль → Мои заказы.</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Order status</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Track your orders in Profile → My Orders section.</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>请在个人资料 → 我的订单部分跟踪您的订单。</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
         <v>1</v>
       </c>
-      <c r="G164" t="n">
+      <c r="O164" t="n">
         <v>57</v>
       </c>
     </row>
@@ -4979,10 +11542,50 @@
           <t>bu uchun siz sahiy seller ilovasini play market yoki app storedan yuklab olishingiz yoki kompyiterdan qidiirib undan kompyuiterda foydalnishingizham mumkin boladi siz ilovani ochib ornatgach unda roytxatdan otibb keyin sozlamalar qismi orqali siz tilni ozgartrib olishingizham mumkin boladi keyin siz bemalol siz dokon yaratish qismi orali dokon yaratib boshlaysiz bunda etibor qilishingiz kerak boaldigan jihatlari quyidagilar yani dokon ochishda unga togri holatda dokon uchun undagi mahsulotlar uchun mos keladigan rasmlarni qoyishingizni sorab qolamiz bu uchun hohasangiz dokon nomimga mos rasm qilib berishni suniy intellerktham qilibberadi va dokon ochishda tariflarni togrilab qoyishingizni sorab qolgan bolar edik yani iloji boricha ozingiz mustaqil holatda suniy intellekt qollashni bosmasdan hamozingiz yozib chiqsangiz boladi yani bu uchun siz dokon ichidagi mahsuloatlar nimalardan iborat boladi shuni qolda yozib chiqishingiz kerak boladi iloji boricha agar qanaqadur savollaringiz bolsa murojaat qilsangiz boladi yoki telegramdan yozsangizham boladi</t>
         </is>
       </c>
-      <c r="F165" t="n">
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>қандай очаман</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>бу учун сиз саҳий seller иловасини play market ёки app storedан юклаб олишингиз ёки компьютердан қидириб ундан компьютерда фойдаланишингиз ҳам мумкин бўлади сиз иловани очиб ўрнатгач унда рўйхатдан ўтиб кейин созламалар қисми орқали сиз тилни ўзгартириб олишингиз ҳам мумкин бўлади кейин сиз бемалол сиз дўкон яратиш қисми орқали дўкон яратиб бошлайсиз бунда эътибор қилишингиз керак бўладиган жиҳатлари қуйидагилар яъни дўкон очишда унга тўғри ҳолатда дўкон учун ундаги маҳсулотлар учун мос келадиган расмларни қўйишингизни сўраб қоламиз бу учун ҳоҳласангиз дўкон номига мос расм қилиб беришни сунъий интеллект ҳам қилиб беради ва дўкон очишда таърифларни тўғрилашингизни сўраб қолган бўлар эдик яъни иложи борича ўзингиз мустақил ҳолатда сунъий интеллект қўллашни босмасдан ҳам ўзингиз ёзиб чиқсангиз бўлади яъни бу учун сиз дўкон ичидаги маҳсулотлар нималардан иборат бўлади шуни қўлда ёзиб чиқишингиз керак бўлади иложи борича агар қандайдир саволларингиз бўлса мурожаат қилсангиз бўлади ёки телеграмдан ёзсангиз ҳам бўлади</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Как открыть магазин?</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Для этого скачайте приложение Sahiy Seller из Play Market или App Store, либо найдите компьютерную версию. После установки зарегистрируйтесь, затем в настройках можете изменить язык. Далее создайте магазин в соответствующем разделе. При создании важно правильно загрузить фото магазина и товаров. При необходимости можно использовать ИИ для генерации фото. Описание пишите самостоятельно, без грубых выражений. Также укажите русское описание. После создания магазина укажите адрес на карте и подтвердите.</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>How to open?</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>For this, download the Sahiy Seller app from Play Market or App Store, or use the computer version. After installing and registering, you can change the language in settings. Then create a store. When creating, make sure to upload appropriate photos. You can use AI to generate photos if needed. Write the description yourself without rude words. Also provide Russian description. After that, mark the address on the map and confirm.</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>如何开店？</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>请从Play Market或App Store下载Sahiy Seller应用，或使用电脑版。安装注册后可在设置中更改语言。然后在相应部分创建商店。创建时请上传合适的商店和商品照片。如需要可使用AI生成照片。描述请自行撰写，避免粗俗语言。同时提供俄文描述。之后在地图标记地址并确认。</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
         <v>1</v>
       </c>
-      <c r="G165" t="n">
+      <c r="O165" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5010,10 +11613,50 @@
           <t>Assalomu alaykum hurmatli mijoz muammoyingiz xal etildimi.</t>
         </is>
       </c>
-      <c r="F166" t="n">
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Салом</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Ассалому алайкум ҳурматли мижоз муаммоингиз ҳал этилдими.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Привет</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум, уважаемый клиент. Ваша проблема решена?</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum dear customer. Has your problem been resolved?</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>你好</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>您好，尊敬的客户。您的问题解决了吗？</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
         <v>1</v>
       </c>
-      <c r="G166" t="n">
+      <c r="O166" t="n">
         <v>85</v>
       </c>
     </row>
@@ -5041,10 +11684,50 @@
           <t>500441360</t>
         </is>
       </c>
-      <c r="F167" t="n">
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Мурожаат учун</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>500441360</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Для обращений</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>500441360</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>For inquiries</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>500441360</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>联系方式</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>500441360</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
         <v>1</v>
       </c>
-      <c r="G167" t="n">
+      <c r="O167" t="n">
         <v>86</v>
       </c>
     </row>
@@ -5072,10 +11755,50 @@
           <t>mahsulotlar buyurtm yo'lga chiqgan muddatingizdan boshlab 13-15 kun ichida keladi va kelganda siz uchun sms xabarnoma boradi telefon raqamingizga .</t>
         </is>
       </c>
-      <c r="F168" t="n">
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Қачон келади</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>маҳсулотлар буюртма йўлга чиққан муддатингиздан бошлаб 13-15 кун ичида келади ва келганда сиз учун смс хабарнома боради телефон рақамингизга.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Когда придёт?</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Товары придут в течение 13-15 дней после отправки заказа. При прибытии вам придёт SMS-уведомление на телефон.</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>When will it arrive?</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Products will arrive within 13-15 days after the order is shipped. You will receive an SMS notification on your phone upon arrival.</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>什么时候到？</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>订单发货后13-15天内到达。到达时您的手机会收到短信通知。</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
         <v>1</v>
       </c>
-      <c r="G168" t="n">
+      <c r="O168" t="n">
         <v>89</v>
       </c>
     </row>
@@ -5103,10 +11826,50 @@
           <t>mahsulotlar buyurtm aqilkgan muddatingizdan boshlab 13-15 kun ichida keladi va kelganda siz uchun sms xabarnoma boradi telefon raqamingizga . murojaat uchun 773229501, 773229501 shunigdek agarda sizda mahsulot kelganida singan yoki kam kelgan holatda bo'lsa buni bizga rasmini hamda xitoycha stikerini tashlab bersangiz bu mahsulotingizni ko'rib chiqamiz va sizga buni ko'rib chiqib xabar beramiz buni qilgan to'lovingizni qaytarib beramiz yoki qayta buyurtma qilib beramiz sizga . agarda mahsulotlaringiz kelmayotgan bo'lsa bu uchun ayni o'sha mahsulotingizni DG raqami yoki uzun tartibli raqamini tashlab bersangiz biz ayni o'sha mahsulotingizni ko'rib beramiz !agarda qabul qilingan degan sms xabarnoma kelgan bolsa bunda demak mahsulotingiz kuryerda berilgan 2 kunda barcha mijozlarga yetkazib berishadi toshkent shahrida . agarda viloyatda bo'lsa bu uchun punktdan olib ketishlik kerak boladi .zakaz uchun taqiqlanmagan mashulotlarni ilovadan tanlab oldindan tolovni amalga oshirishingiz kerak boladi</t>
         </is>
       </c>
-      <c r="F169" t="n">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Умумий маълумот</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>маҳсулотлар буюртма йўлга чиққан муддатингиздан бошлаб 13-15 кун ичида келади ва келганда сиз учун смс хабарнома боради телефон рақамингизга. мурожаат учун 773229501, 773229501 шунингдек агарда сизда маҳсулот келганида синган ёки кам келган ҳолатда бўлса буни бизга расмини ҳамда хитойча стикерини ташлаб берсангиз бу маҳсулотингизни кўриб чиқамиз ва сизга буни кўриб чиқиб хабар берамиз буни қилган тўловингизни қайтариб берамиз ёки қайта буюртма қилиб берамиз сизга. агарда маҳсулотларингиз келмаётган бўлса бу учун айни ўша маҳсулотингизни DG рақами ёки узун тартибли рақамини ташлаб берсангиз биз айни ўша маҳсулотингизни кўриб берамиз! агарда қабул қилинган деган смс хабарнома келган бўлса бунда демак маҳсулотингиз курьерда берилган 2 кунда барча мижозларга етказиб беришади тошкент шаҳрида. агарда вилоятда бўлса бу учун пунктдан олиб кетишлик керак бўлади. заказ учун тақиқланмаган маҳсулотларни иловадан танлаб олдиндан тўловни амалга оширишингиз керак бўлади</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Общая информация</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Товары приходят в течение 13-15 дней после отправки заказа. При прибытии вам придёт SMS. Для обращений: 773229501. Если товар пришёл повреждённым или в неполном комплекте — отправьте фото и китайский стикер, мы рассмотрим и вернём деньги или сделаем повторный заказ. Если заказ не приходит — отправьте DG номер. Если пришло SMS «Принято» — значит товар у курьера, в Ташкенте доставят в течение 2 дней. В регионах забирайте из пункта. Заказывайте только разрешённые товары с предоплатой.</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>General information</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Products arrive within 13-15 days after the order is shipped. You will receive an SMS upon arrival. For inquiries: 773229501. If the product arrives damaged or incomplete, send a photo and Chinese sticker — we will review it and refund or reorder. If the order is not arriving, send the DG number. If you received "Accepted" SMS, the item is with the courier and will be delivered within 2 days in Tashkent. In regions, pick up from the point. Order only permitted items with prepayment.</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>一般信息</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>订单发货后13-15天内到达。到达时会收到短信。联系电话：773229501。如果商品损坏或不完整，请发送照片和中国贴纸，我们会审核并退款或重新下单。如果订单未到达，请发送DG号。如果收到“已接受”短信，说明商品已在快递手中，塔什干市内2天内送达。地区需到自提点取货。请提前支付只订购允许的商品。</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
         <v>1</v>
       </c>
-      <c r="G169" t="n">
+      <c r="O169" t="n">
         <v>90</v>
       </c>
     </row>
@@ -5131,15 +11894,53 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Sahiy Seller — bu sotuvchilar uchun mo‘ljallangan platforma bo‘lib, unda siz o‘z do‘koningizni ro‘yxatdan o‘tkazib, mahsulotlaringizni Sahiy Market ilovasining mahalliy bo‘limida sotishingiz mumkin. 
-Sahiy Market orqali foydalanuvchilar Xitoydan arzon narxlarda mahsulotlar buyurtma qilishlari mumkin, sotuvchilar esa ushbu mahsulotlarni ulgurji xarid qilib, ularni mahalliy bozorda sotish imkoniyatiga ega bo‘ladilar. Platforma to‘liq ishga tushganda esa siz Sahiy mahalliy marketida birinchi sotuvchilardan biri bo‘lish imkoniyatiga ega bo‘lasiz. 
-Hozirda platforma test rejimida ishlamoqda, shu vaqt ichida siz ilova bilan tanishib, barcha imkoniyatlarini o‘rganib chiqishingiz mumkin.</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
+          <t>Sahiy Seller — bu sotuvchilar uchun mo‘ljallangan platforma bo‘lib, unda siz o‘z do‘koningizni ro‘yxatdan o‘tkazib, mahsulotlaringizni Sahiy Market ilovasining mahalliy bo‘limida sotishingiz mumkin. Sahiy Market orqali foydalanuvchilar Xitoydan arzon narxlarda mahsulotlar buyurtma qilishlari mumkin, sotuvchilar esa ushbu mahsulotlarni ulgurji xarid qilib, ularni mahalliy bozorda sotish imkoniyatiga ega bo‘ladilar. Platforma to‘liq ishga tushganda esa siz Sahiy mahalliy marketida birinchi sotuvchilardan biri bo‘lish imkoniyatiga ega bo‘lasiz. Hozirda platforma test rejimida ishlamoqda, shu vaqt ichida siz ilova bilan tanishib, barcha imkoniyatlarini o‘rganib chiqishingiz mumkin.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Селлер умумий маълумот</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Саҳий Seller — бу сотувчилар учун мўлжалланган платформа бўлиб, унда сиз ўз дўконингизни рўйхатдан ўтказиб, маҳсулотларингизни Саҳий Маркет иловасининг маҳаллий бўлимида сотишингиз мумкин. Саҳий Маркет орқали фойдаланувчилар Хитойдан арзон нархларда маҳсулотлар буюртма қилишлари мумкин, сотувчилар эса ушбу маҳсулотларни улгуржи харид қилиб, уларни маҳаллий бозорда сотиш имкониятига эга бўладилар. Платформа тўлиқ ишга тушганда эса сиз Саҳий маҳаллий маркетида биринчи сотувчилардан бири бўлиш имкониятига эга бўласиз. Ҳозирда платформа тест режимида ишламоқда, шу вақт ичида сиз илова билан танишиб, барча имкониятларини ўрганиб чиқишингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Общая информация о Seller</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy Seller — это платформа для продавцов, где вы можете зарегистрировать свой магазин и продавать товары в местном разделе приложения Sahiy Market. Пользователи Sahiy Market могут заказывать товары из Китая по низким ценам, а продавцы имеют возможность закупать их оптом и продавать на локальном рынке. Когда платформа полностью запустится, вы сможете стать одним из первых продавцов на местном рынке Sahiy. Сейчас платформа работает в тестовом режиме, в это время вы можете ознакомиться с приложением и изучить все возможности.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Seller General Information</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy Seller is a platform designed for sellers, where you can register your store and sell your products in the local section of the Sahiy Market app. Users of Sahiy Market can order products from China at low prices, while sellers have the opportunity to buy them wholesale and sell them in the local market. When the platform is fully launched, you will have the opportunity to become one of the first sellers in the local Sahiy market. Currently, the platform is in test mode, during which you can familiarize yourself with the app and explore all its features.</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>Seller 一般信息</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>Sahiy Seller是为卖家设计的平台，您可以在其中注册自己的商店，并在Sahiy Market应用的本地部分销售您的产品。Sahiy Market的用户可以以低价从中国订购产品，而卖家有机会批发购买并在本地市场销售。当平台完全上线时，您将有机会成为Sahiy本地市场的首批卖家之一。目前平台处于测试模式，您可以借此熟悉应用并探索所有功能。</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
         <v>1</v>
       </c>
-      <c r="G170" t="n">
+      <c r="O170" t="n">
         <v>91</v>
       </c>
     </row>
@@ -5167,10 +11968,50 @@
           <t>Mutahasisga yubordim buyurtmangiz holatini bilish uchun operatorlarimizdan javob kuting</t>
         </is>
       </c>
-      <c r="F171" t="n">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Мутахасисга юборилди</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Мутахасисга юбордим буюртмангиз ҳолатини билиш учун операторларимиздан жавоб кутинг</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Отправлено специалисту</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Отправил специалисту. Ожидайте ответа от наших операторов по статусу вашего заказа.</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Sent to specialist</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Sent to specialist. Wait for a response from our operators regarding your order status.</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>已发送给专家</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>已发送给专家。请等待我们的客服回复您的订单状态。</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
         <v>1</v>
       </c>
-      <c r="G171" t="n">
+      <c r="O171" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5198,10 +12039,50 @@
           <t>Assalomu alaykum. Hurmatli mijoz buyurtmalar yo'lga chiqarib yuborilgan vaqtdan boshlab 15 kunda yetib keladi</t>
         </is>
       </c>
-      <c r="F172" t="n">
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>буюртмалар етиб келиш вақти</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Ассалому алайкум. Ҳурматли мижоз буюртмалар йўлга чиқариб юборилган вақтдан бошлаб 15 кунда етиб келади</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Время прибытия заказов</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум. Уважаемый клиент, заказы прибудут в течение 15 дней после отправки.</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Order arrival time</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum. Dear customer, orders will arrive within 15 days after shipment.</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>订单到达时间</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>您好，尊敬的客户，订单发货后将在15天内到达。</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
         <v>1</v>
       </c>
-      <c r="G172" t="n">
+      <c r="O172" t="n">
         <v>93</v>
       </c>
     </row>
@@ -5229,10 +12110,50 @@
           <t>Assalomu alaykum. Hurmatli mijoz kerltirilgan noqulayliklar va kechikishlar uchun uzr so'raymiz. ushbu buyurtmangiz muammosi haqida masul xodimga xabar berildi. tez orada muammoingiz hal qilinadi Xudo xoxlasa</t>
         </is>
       </c>
-      <c r="F173" t="n">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Ноқулайликлар учун узр</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Ассалому алайкум. Ҳурматли мижоз келтирилган ноқулайликлар ва кечикишлар учун узр сўраймиз. ушбу буюртмангиз муаммоси ҳақида масъул ходимга хабар берилди. тез орада муаммоингиз ҳал қилинади Худо хоҳласа</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Извиняемся за неудобства</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум. Уважаемый клиент, приносим извинения за причинённые неудобства и задержки. О вашей проблеме с заказом сообщено ответственному сотруднику. В ближайшее время ваша проблема будет решена, если будет угодно Богу.</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Sorry for the inconvenience</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum. Dear customer, we apologize for the inconvenience and delays caused. We have informed the responsible employee about the issue with your order. Your problem will be resolved soon, God willing.</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>抱歉给您带来不便</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>您好，尊敬的客户，对于给您带来的不便和延误，我们深表歉意。关于您订单的问题已通知相关负责人。您的问題很快就会解决，如果真主愿意。</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
         <v>1</v>
       </c>
-      <c r="G173" t="n">
+      <c r="O173" t="n">
         <v>94</v>
       </c>
     </row>
@@ -5260,10 +12181,50 @@
           <t>Assalomu alaykum. buyurtmalaringiz xolatini tekshirmoqdamiz. tez orada aniqlashtirib sizga xabar beramiz. Kechikishlar uchun uzr.</t>
         </is>
       </c>
-      <c r="F174" t="n">
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>текширамиз 2</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Ассалому алайкум. буюртмаларингиз ҳолатини текширмоқдамиз. тез орада аниқлаштириб сизга хабар берамиз. Кечикишлар учун узр.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Проверяем 2</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум. Мы проверяем статус ваших заказов. В ближайшее время уточним и сообщим вам. Извиняемся за задержки.</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>We are checking 2</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum. We are checking the status of your orders. We will clarify and inform you soon. Sorry for the delays.</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>我们正在检查 2</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>您好，我们正在检查您的订单状态。很快会确认并通知您。对于延误我们表示歉意。</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
         <v>1</v>
       </c>
-      <c r="G174" t="n">
+      <c r="O174" t="n">
         <v>95</v>
       </c>
     </row>
@@ -5291,10 +12252,50 @@
           <t>Ulgurji savdo bu asosan biznesmenlar uchun. Bunda siz mahsulotlarni xitoydagi arginal narxda sotib olasiz, unga bizdan ustama qo'shimcha narx qo'shilmaydi. ammo har bir mahsulotning kargo xizmati bo'ladi. MASALAN TASAVVUR QILING MEN HOZIR toshkentdan 5ming so'mga semichka sotibolaman. Uni vodiyga oborib sotaman. O'zimdan semichkaning narxi ustiga yana ikkiming so'm qo'shaman+ toshkentdan vodiyga olib kelganim uchun yo'l haqqi o'laroq yana ming so'm qo'shaman= semichkaning narxi 8ming bo'lib qoladi. Bu B2C savdo. B2Bda esa men semichkaga faqat ming so'm yo'l haqqi qo'shaman xolos.</t>
         </is>
       </c>
-      <c r="F175" t="n">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>улгуржи савдо ҳақида2</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Улгуржи савдо бу асосан бизнесменлар учун. Бунда сиз маҳсулотларни хитойдаги арзон нархда сотиб оласиз, унга биздан устама қўшимча нарх қўшилмайди. аммо ҳар бир маҳсулотнинг карго хизмати бўлади. МАСАЛАН ТАСАВВУР ҚИЛИНГ МЕН ҲОЗИР тошкентдан 5минг сўмга семичка сотиб оламан. Уни водийга обориб сотаман. Ўзимдан семичканинг нархи устига яна иккиминг сўм қўшаман + тошкентдан водийга олиб келганим учун йўл ҳаққи ўлароқ яна минг сўм қўшаман = семичканинг нархи 8минг бўлиб қолади. Бу B2C савдо. B2Bда эса мен семичкага фақат минг сўм йўл ҳаққи қўшаман холос.</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Об оптовой торговле 2</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Оптовая торговля в основном для бизнесменов. Здесь вы покупаете товары по цене из Китая без нашей наценки. Но за каждый товар будет оплата карго. Например: я покупаю семечки в Ташкенте за 5000 сум, везу в долину и продаю, добавляя свою наценку 2000 + 1000 за дорогу = 8000 сум. Это B2C. В B2B я добавляю только 1000 сум за дорогу.</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>About wholesale trade 2</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Wholesale trade is mainly for businessmen. Here you buy products at the original price from China without our markup. However, there is a cargo fee for each product. For example: I buy seeds in Tashkent for 5000 sum, take them to the valley and sell them, adding my markup of 2000 + 1000 for transportation = 8000 sum. This is B2C. In B2B, I only add 1000 sum for transportation.</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>关于批发贸易2</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>批发贸易主要面向商人。在这里您可以按中国原价购买商品，我们不加价。但每件商品都有货物运输费。例如：我在塔什干以5000苏姆买瓜子，运到山谷出售，加上自己的2000苏姆利润 + 1000苏姆运费 = 8000苏姆。这是B2C。在B2B中，我只加1000苏姆的运费。</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
         <v>1</v>
       </c>
-      <c r="G175" t="n">
+      <c r="O175" t="n">
         <v>96</v>
       </c>
     </row>
@@ -5322,10 +12323,50 @@
           <t>Assalomu alaykum. Hurmatli mijoz sizninng buyurtmangizni topshirishi uchun sizga kuryerlarimiz telefon qilib bog'lana olishmagan ekan. Siz bog'lanish raqami sifatida ilovada qoldirgan raqamingizga tusha olishmagan. Iltimos siz bilan bog'lana olishimiz uchun birzga ayni damda faol ishlayotgan raqam yozib qoldirsngiz.</t>
         </is>
       </c>
-      <c r="F176" t="n">
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>рақам сўрови</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Ассалому алайкум. Ҳурматли мижоз сизнинг буюртмангизни топшириши учун сизга курьерларимиз телефон қилиб боғлана олишмаган экан. Сиз боғланиш рақами сифатида иловада қолдирган рақамингизга туша олишмаган. Илтимос сиз билан боғлана олишимиз учун бирга айни дамда фаол ишлаётган рақам ёзиб қолдирсангиз.</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Запрос номера</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Ассаламу алейкум. Уважаемый клиент, наши курьеры не смогли дозвониться вам для вручения заказа. Номер, который вы указали в приложении, оказался недоступен. Пожалуйста, оставьте актуальный номер, по которому мы сможем с вами связаться.</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Phone number request</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Assalomu alaykum. Dear customer, our couriers could not reach you to deliver your order. The number you left in the app was unreachable. Please leave an active number so we can contact you.</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>电话号码请求</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>您好，尊敬的客户，我们的快递员无法联系到您交付订单。您在应用中留的号码无法接通。请留下当前有效的号码，以便我们与您联系。</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
         <v>1</v>
       </c>
-      <c r="G176" t="n">
+      <c r="O176" t="n">
         <v>99</v>
       </c>
     </row>
@@ -5353,10 +12394,50 @@
           <t>Ro'yxatdan o'tish uchun asosiy sahifadagi "Kirish/Ro'yxatdan o'tish" tugmasini bosing. Telefon raqamingizni kiriting va SMS orqali kelgan tasdiqlash kodini kiriting. So'ngra shaxsiy ma'lumotlaringizni to'ldiring.</t>
         </is>
       </c>
-      <c r="F177" t="n">
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Қандай қилиб рўйхатдан ўтишим мумкин?</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Рўйхатдан ўтиш учун асосий саҳифадаги "Кириш/Рўйхатдан ўтиш" тугмасини босинг. Телефон рақамингизни киритинг ва СМС орқали келган тасдиқлаш кодини киритинг. Сўнгра шахсий маълумотларингизни тўлдиринг.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Как мне зарегистрироваться?</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Для регистрации нажмите кнопку «Вход/Регистрация» на главной странице. Введите свой номер телефона, введите код подтверждения из SMS, затем заполните личные данные.</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>How can I register?</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>To register, click the "Login/Register" button on the main page. Enter your phone number, enter the confirmation code from SMS, then fill in your personal information.</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>如何注册？</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>要注册，请点击主页上的“登录/注册”按钮。输入您的手机号码，输入短信验证码，然后填写个人信息。</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
         <v>2</v>
       </c>
-      <c r="G177" t="n">
+      <c r="O177" t="n">
         <v>66</v>
       </c>
     </row>
@@ -5384,10 +12465,50 @@
           <t>Kerakli mahsulotni toping, "Savatga qo'shish" tugmasini bosing. Savatga o'tib, buyurtmani rasmiylashtirishni boshlang. Yetkazib berish manzili va to'lov usulini tanlang, so'ngra buyurtmani tasdiqlang.</t>
         </is>
       </c>
-      <c r="F178" t="n">
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулотни қандай буюртма қилишим мумкин?</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Керакли маҳсулотни топинг, "Саватга қўшиш" тугмасини босинг. Саватга ўтиб, буюртмани расмийлаштиришни бошланг. Йетказиб бериш манзили ва тўлов усулини танланг, сўнгра буюртмани тасдиқланг.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Как мне заказать товар?</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Найдите нужный товар, нажмите кнопку «Добавить в корзину». Перейдите в корзину и начните оформление заказа. Выберите адрес доставки и способ оплаты, затем подтвердите заказ.</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>How can I order a product?</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Find the desired product, click "Add to Cart". Go to the cart and start the order process. Select the delivery address and payment method, then confirm the order.</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>如何下单商品？</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>找到所需商品，点击“加入购物车”。进入购物车开始下单流程。选择配送地址和支付方式，然后确认订单。</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
         <v>2</v>
       </c>
-      <c r="G178" t="n">
+      <c r="O178" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5415,10 +12536,50 @@
           <t>Biz quyidagi to'lov usullarini qo'llab-quvvatlaymiz: bank kartalari (UzCard, Humo), Click, Payme va Paynet to'lov tizimlari.</t>
         </is>
       </c>
-      <c r="F179" t="n">
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Қандай тўлов усуллари мавжуд?</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Биз қуйидаги тўлов усулларини қўллаб-қувватлаймиз: банк карталари (UzCard, Humo), Click, Payme ва Paynet тўлов тизимлари.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>Какие способы оплаты доступны?</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Мы поддерживаем следующие способы оплаты: банковские карты (UzCard, Humo), Click, Payme и Paynet.</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>What payment methods are available?</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>We support the following payment methods: bank cards (UzCard, Humo), Click, Payme and Paynet payment systems.</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>有哪些支付方式？</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>我们支持以下支付方式：银行卡（UzCard、Humo）、Click、Payme和Paynet支付系统。</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
         <v>2</v>
       </c>
-      <c r="G179" t="n">
+      <c r="O179" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5446,10 +12607,50 @@
           <t>O'zbekiston bo'ylab standart yetkazib berish 2-5 kun ichida amalga oshiriladi. Toshkent shahri bo'yicha 1-2 kun. Xitoydan buyurtma qilingan mahsulotlar uchun 15-25 kun. Tezkor yetkazib berish xizmati ham mavjud.</t>
         </is>
       </c>
-      <c r="F180" t="n">
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Йетказиб бериш қанча вақт олади?</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Ўзбекистон бўйлаб стандарт йетказиб бериш 2-5 кун ичида амалга оширилади. Тошкент шаҳри бўйича 1-2 кун. Хитойдан буюртма қилинган маҳсулотлар учун 15-25 кун. Тезкор йетказиб бериш хизмати ҳам мавжуд.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Сколько времени занимает доставка?</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Стандартная доставка по Узбекистану занимает 2-5 дней. По Ташкенту — 1-2 дня. Для товаров из Китая — 15-25 дней. Также доступна экспресс-доставка.</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>How long does delivery take?</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Standard delivery across Uzbekistan takes 2-5 days. Within Tashkent city — 1-2 days. For products ordered from China — 15-25 days. Express delivery service is also available.</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>配送需要多长时间？</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>乌兹别克斯坦境内标准配送需要2-5天。塔什干市内1-2天。从中国订购的商品需要15-25天。还提供快速配送服务。</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
         <v>2</v>
       </c>
-      <c r="G180" t="n">
+      <c r="O180" t="n">
         <v>69</v>
       </c>
     </row>
@@ -5477,10 +12678,50 @@
           <t>Buyurtmani kuzatish uchun "Mening buyurtmalarim" bo'limiga o'ting. Har bir buyurtma uchun kuzatish raqami va joriy holat ko'rsatiladi. Shuningdek, SMS orqali holat haqida xabarnomalar olasiz.</t>
         </is>
       </c>
-      <c r="F181" t="n">
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани қандай кузатишим мумкин?</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Буюртмани кузатиш учун "Менинг буюртмаларим" бўлимига ўтинг. Ҳар бир буюртма учун кузатиш рақами ва жорий ҳолат кўрсатилади. Шунингдек, СМС орқали ҳолат ҳақида хабарномалар оласиз.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Как отслеживать заказ?</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Перейдите в раздел «Мои заказы». Для каждого заказа отображается трекинг-номер и текущий статус. Также вы будете получать SMS-уведомления о статусе.</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>How can I track my order?</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Go to the "My Orders" section to track your order. Each order shows a tracking number and current status. You will also receive SMS notifications about the status.</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>如何跟踪订单？</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>进入“我的订单”部分跟踪订单。每个订单都会显示跟踪号和当前状态。您还会收到关于状态的短信通知。</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
         <v>2</v>
       </c>
-      <c r="G181" t="n">
+      <c r="O181" t="n">
         <v>73</v>
       </c>
     </row>
@@ -5508,10 +12749,50 @@
           <t>SAHIY SELLER - bu mahalliy sotuvchilar uchun professional platforma. O'z mahsulotlaringizni platformada sotishingiz va keng auditoriyaga yetkazishingiz mumkun. Batafsil ma'lumot uchun SAHIY SELLER bo'limiga o'ting.</t>
         </is>
       </c>
-      <c r="F182" t="n">
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>САҲИЙ СЕЛЛЕР нима?</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>САҲИЙ СЕЛЛЕР - бу маҳаллий сотувчилар учун профессионал платформа. Ўз маҳсулотларингизни платформада сотишингиз ва кенг аудиторияга етказишингиз мумкин. Батафсил маълумот учун САҲИЙ СЕЛЛЕР бўлимига ўтинг.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Что такое SAHIY SELLER?</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>SAHIY SELLER — это профессиональная платформа для местных продавцов. Вы можете продавать свои товары на платформе и охватывать широкую аудиторию. Подробная информация в разделе SAHIY SELLER.</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>What is SAHIY SELLER?</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>SAHIY SELLER is a professional platform for local sellers. You can sell your products on the platform and reach a wide audience. For detailed information, go to the SAHIY SELLER section.</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>SAHIY SELLER是什么？</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>SAHIY SELLER是为本地卖家设计的专业平台。您可以在平台上销售您的产品并触达更广泛的受众。详细信息请进入SAHIY SELLER部分。</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
         <v>2</v>
       </c>
-      <c r="G182" t="n">
+      <c r="O182" t="n">
         <v>75</v>
       </c>
     </row>
@@ -5539,10 +12820,50 @@
           <t>Mahsulot narxi valyuta kursi, chegirmalar, aksiyalar va yetkazib beruvchi tomonidan o'zgarishlar tufayli o'zgarishi mumkun. Joriy narx savatchada ko'rsatiladi.</t>
         </is>
       </c>
-      <c r="F183" t="n">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот нархи нима учун ўзгаради?</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот нархи валюта курси, чегирмалар, аксиялар ва етказиб берувчи томонидан ўзгаришлар туфайли ўзгариши мумкин. Жорий нарх саватчада кўрсатилади.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Почему меняется цена товара?</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Цена товара может меняться из-за курса валют, скидок, акций и изменений со стороны поставщика. Актуальная цена отображается в корзине.</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Why does the product price change?</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>The product price may change due to currency rates, discounts, promotions, and changes by the supplier. The current price is shown in the cart.</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>产品价格为什么会变化？</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>产品价格可能因汇率、折扣、促销和供应商变更而变化。当前价格显示在购物车中。</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
         <v>2</v>
       </c>
-      <c r="G183" t="n">
+      <c r="O183" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5570,10 +12891,50 @@
           <t>Mahsulot izlash uchun asosiy sahifadagi qidiruv maydonini ishlating. Kalit so'zlar, kategoriyalar yoki rasm orqali qidirishingiz mumkun. Filterlardan foydalanib natijalarni aniqlashtirishingiz mumkin.</t>
         </is>
       </c>
-      <c r="F184" t="n">
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Қандай қилиб маҳсулот излашим мумкин?</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот излаш учун асосий саҳифадаги қидирув майдонини ишлатинг. Калит сўзлар, категориялар ёки расм орқали қидиришингиз мумкин. Фильтерлардан фойдаланиб натижаларни аниқлаштиришингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Как искать товары?</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Используйте поле поиска на главной странице. Вы можете искать по ключевым словам, категориям или по фото. Используйте фильтры для уточнения результатов.</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>How can I search for a product?</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Use the search field on the main page. You can search by keywords, categories, or image. Use filters to refine the results.</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>如何搜索商品？</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>使用主页上的搜索框。您可以通过关键词、类别或图片搜索。使用筛选器可以精炼结果。</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
         <v>2</v>
       </c>
-      <c r="G184" t="n">
+      <c r="O184" t="n">
         <v>77</v>
       </c>
     </row>
@@ -5601,10 +12962,50 @@
           <t>Biz ikki faktorli autentifikatsiya, shifrlangan ma'lumotlar saqlash va xavfsiz to'lov tizimlaridan foydalanamiz. Parolingizni hech kimga bermang va shubhali harakatlar haqida darhol xabar bering.</t>
         </is>
       </c>
-      <c r="F185" t="n">
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Аккаунтим хавфсизлиги қандай таъминланади?</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Биз икки факторли аутентификация, шифрланган маълумотлар сақлаш ва хавфсиз тўлов тизимларидан фойдаланамиз. Паролингизни ҳеч кимга берманг ва шубҳали ҳаракатлар ҳақида дарҳол хабар беринг.</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Как обеспечивается безопасность моего аккаунта?</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Мы используем двухфакторную аутентификацию, шифрование данных и безопасные платёжные системы. Никому не сообщайте свой пароль и сразу сообщайте о подозрительных действиях.</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>How is my account security ensured?</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>We use two-factor authentication, encrypted data storage, and secure payment systems. Do not share your password with anyone and report any suspicious activity immediately.</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>如何保障我的账户安全？</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>我们使用双重认证、加密数据存储和安全支付系统。请勿将密码告诉任何人，并立即报告任何可疑行为。</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
         <v>2</v>
       </c>
-      <c r="G185" t="n">
+      <c r="O185" t="n">
         <v>78</v>
       </c>
     </row>
@@ -5632,10 +13033,50 @@
           <t>Qo'llab-quvvatlash xizmatiga "Yordam markazi" bo'limidan murojaat qiling.</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Қўллаб-қувватлаш хизматига қандай мурожаат қилишим мумкин?</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Қўллаб-қувватлаш хизматига "Ёрдам маркази" бўлимидан мурожаат қилинг.</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Как обратиться в службу поддержки?</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Обратитесь в службу поддержки через раздел «Центр помощи».</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>How can I contact customer support?</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Contact customer support through the "Help Center" section.</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>如何联系客服？</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>请通过“帮助中心”部分联系客服。</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
         <v>2</v>
       </c>
-      <c r="G186" t="n">
+      <c r="O186" t="n">
         <v>79</v>
       </c>
     </row>
@@ -5663,10 +13104,50 @@
           <t>Ha, ko'plab mahsulotlar ishlab chiqaruvchi kafolatiga ega. Kafolat muddati mahsulot turiga bog'liq. Batafsil ma'lumotni mahsulot sahifasidan toping.</t>
         </is>
       </c>
-      <c r="F187" t="n">
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот кафолати борми?</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Ҳа, кўплаб маҳсулотлар ишлаб чиқарувчи кафолатига эга. Кафолат муддати маҳсулот турига боғлиқ. Батафсил маълумотни маҳсулот саҳифасидан топинг.</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Есть ли гарантия на товар?</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Да, многие товары имеют гарантию производителя. Срок гарантии зависит от типа товара. Подробную информацию можно найти на странице товара.</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>Is there a product warranty?</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Yes, many products have a manufacturer's warranty. The warranty period depends on the type of product. Detailed information can be found on the product page.</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>产品有保修吗？</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>是的，许多产品有制造商保修。保修期取决于产品类型。详细信息请在产品页面查看。</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
         <v>2</v>
       </c>
-      <c r="G187" t="n">
+      <c r="O187" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5694,10 +13175,50 @@
           <t>Manzilni o'zgartirish uchun "Shaxsiy ma'lumotlar" bo'limidagi "Mening manzillarim" sahifasiga o'ting. Yangi manzil qo'shishingiz yoki mavjud manzilni tahrirlashingiz mumkin.</t>
         </is>
       </c>
-      <c r="F188" t="n">
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Манзилимни қандай ўзгартиришим мумкин?</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Манзилни ўзгартириш учун "Шахсий маълумотлар" бўлимидаги "Менинг манзилларим" саҳифасига ўтинг. Янги манзил қўшишингиз ёки мавжуд манзилни таҳрирлашингиз мумкин.</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Как изменить мой адрес?</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Чтобы изменить адрес, перейдите в раздел «Личные данные» → страница «Мои адреса». Вы можете добавить новый адрес или отредактировать существующий.</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>How can I change my address?</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>To change your address, go to the "Personal Information" section and then to the "My Addresses" page. You can add a new address or edit an existing one.</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>如何更改我的地址？</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>要更改地址，请进入“个人信息”部分，然后进入“我的地址”页面。您可以添加新地址或编辑现有地址。</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
         <v>2</v>
       </c>
-      <c r="G188" t="n">
+      <c r="O188" t="n">
         <v>81</v>
       </c>
     </row>
@@ -5725,10 +13246,50 @@
           <t>Chegirmalar va aksiyalar haqida push-bildirishnomalar orqali xabar beramiz.</t>
         </is>
       </c>
-      <c r="F189" t="n">
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Чегирмалар ва аксиялар ҳақида қандай билиб оламан?</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Чегирмалар ва аксиялар ҳақида пуш-билдиришномалар орқали хабар берамиз.</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>Как узнать о скидках и акциях?</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>Мы информируем о скидках и акциях через push-уведомления.</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>How can I learn about discounts and promotions?</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>We inform about discounts and promotions through push notifications.</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>如何了解折扣和促销活动？</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>我们通过推送通知告知折扣和促销活动。</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
         <v>2</v>
       </c>
-      <c r="G189" t="n">
+      <c r="O189" t="n">
         <v>82</v>
       </c>
     </row>
@@ -5756,10 +13317,50 @@
           <t>Barcha mahsulotlar ishonchli yetkazib beruvchilardan keladi. Ko'pchilik mahsulotlarda haqiqiylik sertifikatlari va QR-kodlari mavjud. Agar shubhangiz bo'lsa, qo'llab-quvvatlash xizmatiga murojaat qiling.</t>
         </is>
       </c>
-      <c r="F190" t="n">
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Маҳсулот ҳақиқийлигини қандай текширишим мумкин?</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Барча маҳсулотлар ишончли етказиб берувчилардан келади. Кўпчилик маҳсулотларда ҳақиқийлик сертификатлари ва QR-кодлари мавжуд. Агар шубҳангиз бўлса, қўллаб-қувватлаш хизматига мурожаат қилинг.</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Как проверить подлинность товара?</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>Все товары поступают от надёжных поставщиков. На большинстве товаров есть сертификаты подлинности и QR-коды. Если у вас есть сомнения, обратитесь в службу поддержки.</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>How can I check the authenticity of the product?</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>All products come from reliable suppliers. Most products have authenticity certificates and QR codes. If you have any doubts, contact customer support.</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>如何验证产品真伪？</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>所有产品均来自可靠供应商。大多数产品有真伪证书和二维码。如果有疑问，请联系客服。</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
         <v>2</v>
       </c>
-      <c r="G190" t="n">
+      <c r="O190" t="n">
         <v>83</v>
       </c>
     </row>
